--- a/inp_Excel/ana_clienti.xlsx
+++ b/inp_Excel/ana_clienti.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8008" uniqueCount="2712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8007" uniqueCount="2715">
   <si>
     <t>CLIENTE_ID</t>
   </si>
@@ -6512,6 +6512,30 @@
     <t>ALLERGIA A BACTRIM</t>
   </si>
   <si>
+    <t>MJEKRA</t>
+  </si>
+  <si>
+    <t>ELIS</t>
+  </si>
+  <si>
+    <t>VIA RIALTA 14</t>
+  </si>
+  <si>
+    <t>79123760</t>
+  </si>
+  <si>
+    <t>mjekra.elis@gmail.com</t>
+  </si>
+  <si>
+    <t>MJKLSE86D0SZ100X</t>
+  </si>
+  <si>
+    <t>CA52632DM</t>
+  </si>
+  <si>
+    <t>MINISTERO DELL'INTERNO</t>
+  </si>
+  <si>
     <t>arrigoni.andrea10@gmail.com</t>
   </si>
   <si>
@@ -7145,397 +7169,382 @@
     <t>COMUNE DI UDINE</t>
   </si>
   <si>
-    <t>3386190437</t>
-  </si>
-  <si>
-    <t>colombor0525@gmail.com</t>
-  </si>
-  <si>
-    <t>CLMRRT64E65A794E</t>
-  </si>
-  <si>
-    <t>CA55736PG</t>
+    <t xml:space="preserve">PAOLI </t>
+  </si>
+  <si>
+    <t>FRAZ. GATTAIA 110</t>
+  </si>
+  <si>
+    <t>3351236465</t>
+  </si>
+  <si>
+    <t>duepi902@msn.com</t>
+  </si>
+  <si>
+    <t>PLAPLA52H06D575N</t>
+  </si>
+  <si>
+    <t>CA92174HY</t>
+  </si>
+  <si>
+    <t>CAMPO NELL'ELBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTELLI </t>
+  </si>
+  <si>
+    <t>FULVIA</t>
+  </si>
+  <si>
+    <t>3338446780</t>
+  </si>
+  <si>
+    <t>mart.fulvia@gmail.com</t>
+  </si>
+  <si>
+    <t>MRTFLV55D60D575R</t>
+  </si>
+  <si>
+    <t>CA55784LQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMUNE DI VICCHIO </t>
+  </si>
+  <si>
+    <t>BOTTONI</t>
+  </si>
+  <si>
+    <t>VIA PAOLO DI DONO 145</t>
+  </si>
+  <si>
+    <t>3387212487</t>
+  </si>
+  <si>
+    <t>franz.bottoni@alice.it</t>
+  </si>
+  <si>
+    <t>BTTFNC57H11H501O</t>
+  </si>
+  <si>
+    <t>U151P0700F</t>
+  </si>
+  <si>
+    <t>MIT-UCO</t>
+  </si>
+  <si>
+    <t>FIORE</t>
+  </si>
+  <si>
+    <t>VIALE ALDO BALLARIN 138</t>
+  </si>
+  <si>
+    <t>3471936906</t>
+  </si>
+  <si>
+    <t>pfiore1009@gmail.com</t>
+  </si>
+  <si>
+    <t>FRIPLA65P50H501N</t>
+  </si>
+  <si>
+    <t>U178Z1418X</t>
+  </si>
+  <si>
+    <t>GRUOSSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO </t>
+  </si>
+  <si>
+    <t>VIA SALVO RANDONE</t>
+  </si>
+  <si>
+    <t>3335268050</t>
+  </si>
+  <si>
+    <t>ciccioni_2007@libero.it</t>
+  </si>
+  <si>
+    <t>GRSFBA83D29H501R</t>
+  </si>
+  <si>
+    <t>CA50195EX</t>
+  </si>
+  <si>
+    <t>MINISTERO INTERNO</t>
+  </si>
+  <si>
+    <t>PALLINI</t>
+  </si>
+  <si>
+    <t>VIA VECCHIA DI POZZOLATICO 17</t>
+  </si>
+  <si>
+    <t>3332753430</t>
+  </si>
+  <si>
+    <t>robertopallini2@gmail.com</t>
+  </si>
+  <si>
+    <t>PLLRRT55L25D612T</t>
+  </si>
+  <si>
+    <t>CA70380IT</t>
+  </si>
+  <si>
+    <t>COMUNE DI FIRENZE</t>
+  </si>
+  <si>
+    <t>INTOLLERANZA AGLIO</t>
+  </si>
+  <si>
+    <t>GIARRE'</t>
+  </si>
+  <si>
+    <t>GIOVANNA</t>
+  </si>
+  <si>
+    <t>3388812477</t>
+  </si>
+  <si>
+    <t>giovanna.giarre@gmail.com</t>
+  </si>
+  <si>
+    <t>GRRGNN57D65G843F</t>
+  </si>
+  <si>
+    <t>CA95518TC</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>VIA CASTELLO 12</t>
+  </si>
+  <si>
+    <t>3932666173</t>
+  </si>
+  <si>
+    <t>omar.belotti73@gmail.com</t>
+  </si>
+  <si>
+    <t>BLTMRO73M07H910O</t>
+  </si>
+  <si>
+    <t>CA36105WL</t>
+  </si>
+  <si>
+    <t>PREITE</t>
+  </si>
+  <si>
+    <t>MARCO GIACOMO</t>
+  </si>
+  <si>
+    <t>VIA DANTE ALIGHIERI 27</t>
+  </si>
+  <si>
+    <t>3931231234</t>
+  </si>
+  <si>
+    <t>eletraessere_srl@yahoo.it</t>
+  </si>
+  <si>
+    <t>PRTMCG72T15H910E</t>
+  </si>
+  <si>
+    <t>CA83782IN</t>
+  </si>
+  <si>
+    <t>COMUNE ALMENNO SAN BARTOLOMEO</t>
+  </si>
+  <si>
+    <t>POLLINI</t>
+  </si>
+  <si>
+    <t>VIA BEATO NICONE N.13</t>
+  </si>
+  <si>
+    <t>3396588988</t>
+  </si>
+  <si>
+    <t>asmpollini@libero.it</t>
+  </si>
+  <si>
+    <t>PLLMRC59C16F205C</t>
+  </si>
+  <si>
+    <t>AZ0928893</t>
+  </si>
+  <si>
+    <t>BESOZZO</t>
+  </si>
+  <si>
+    <t>DI GIROLAMO</t>
+  </si>
+  <si>
+    <t>3442948830</t>
+  </si>
+  <si>
+    <t>info@limotaximilano.com</t>
+  </si>
+  <si>
+    <t>DGRSRG70H14I819Q</t>
+  </si>
+  <si>
+    <t>CA79235AP</t>
+  </si>
+  <si>
+    <t>CASSANO MAGNAGO</t>
+  </si>
+  <si>
+    <t>MOSTARDA</t>
+  </si>
+  <si>
+    <t>VIA ROMA 46</t>
+  </si>
+  <si>
+    <t>3892717592</t>
+  </si>
+  <si>
+    <t>claudiomostarda@gmail.com</t>
+  </si>
+  <si>
+    <t>MSTCLD63E14H501M</t>
+  </si>
+  <si>
+    <t>CA702806QH</t>
+  </si>
+  <si>
+    <t>RIVODUTRI</t>
+  </si>
+  <si>
+    <t>MARIANI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIANLUIGI </t>
+  </si>
+  <si>
+    <t>3248608126</t>
+  </si>
+  <si>
+    <t>gianluigimariani89@libero.it</t>
+  </si>
+  <si>
+    <t>MRNGLG89R27F839S</t>
+  </si>
+  <si>
+    <t>CA16303HF</t>
+  </si>
+  <si>
+    <t>COMUNE CUNEO</t>
+  </si>
+  <si>
+    <t>NULLA</t>
+  </si>
+  <si>
+    <t>CROCIANI</t>
+  </si>
+  <si>
+    <t>VIA BARTOLOMEO VANZETTI 15</t>
+  </si>
+  <si>
+    <t>3285966715</t>
+  </si>
+  <si>
+    <t>matteocrociani2@gmail.com</t>
+  </si>
+  <si>
+    <t>CRCMTT83H15D704Y</t>
+  </si>
+  <si>
+    <t>CA57525QV</t>
+  </si>
+  <si>
+    <t>COMUNE DI FORLI'</t>
+  </si>
+  <si>
+    <t>BONAFE'</t>
+  </si>
+  <si>
+    <t>39349784058</t>
+  </si>
+  <si>
+    <t>benedetta.bonafe@gmail.com</t>
+  </si>
+  <si>
+    <t>BNFBXX88B66E379G</t>
+  </si>
+  <si>
+    <t>CA30471FS</t>
+  </si>
+  <si>
+    <t>COMUNE DI IVREA</t>
+  </si>
+  <si>
+    <t>DI VINCENZO</t>
+  </si>
+  <si>
+    <t>MARIA ENZA</t>
+  </si>
+  <si>
+    <t>3393729169</t>
+  </si>
+  <si>
+    <t>mari.divincenzo@gmail.com</t>
+  </si>
+  <si>
+    <t>DVNMNZ68L57A479J</t>
+  </si>
+  <si>
+    <t>4614584AA</t>
+  </si>
+  <si>
+    <t>SCARLASSARE</t>
+  </si>
+  <si>
+    <t>3351360543</t>
+  </si>
+  <si>
+    <t>laurascarlassare66@gmail.com</t>
+  </si>
+  <si>
+    <t>SCRLRA66M41I531E</t>
+  </si>
+  <si>
+    <t>CA79722HN</t>
+  </si>
+  <si>
+    <t>GELFI</t>
+  </si>
+  <si>
+    <t>mauriziogelfi@hotmail.it</t>
+  </si>
+  <si>
+    <t>U15V19957N</t>
+  </si>
+  <si>
+    <t>MIMOUNE</t>
+  </si>
+  <si>
+    <t>NACIRI</t>
+  </si>
+  <si>
+    <t>VIA ALESSANDRO VOLTA, 1</t>
+  </si>
+  <si>
+    <t>35192681</t>
+  </si>
+  <si>
+    <t>nacirimimoune9@gmail.com</t>
+  </si>
+  <si>
+    <t>NCRMMN06T09Z330V</t>
+  </si>
+  <si>
+    <t>CA81582RN</t>
   </si>
   <si>
     <t>COMUNE DI BERGAMO</t>
-  </si>
-  <si>
-    <t>ALLERGIA A CRISTACEI E PESCI DI GROSSA DIMENSIONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAOLI </t>
-  </si>
-  <si>
-    <t>FRAZ. GATTAIA 110</t>
-  </si>
-  <si>
-    <t>3351236465</t>
-  </si>
-  <si>
-    <t>duepi902@msn.com</t>
-  </si>
-  <si>
-    <t>PLAPLA52H06D575N</t>
-  </si>
-  <si>
-    <t>CA92174HY</t>
-  </si>
-  <si>
-    <t>CAMPO NELL'ELBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARTELLI </t>
-  </si>
-  <si>
-    <t>FULVIA</t>
-  </si>
-  <si>
-    <t>3338446780</t>
-  </si>
-  <si>
-    <t>mart.fulvia@gmail.com</t>
-  </si>
-  <si>
-    <t>MRTFLV55D60D575R</t>
-  </si>
-  <si>
-    <t>CA55784LQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMUNE DI VICCHIO </t>
-  </si>
-  <si>
-    <t>BOTTONI</t>
-  </si>
-  <si>
-    <t>VIA PAOLO DI DONO 145</t>
-  </si>
-  <si>
-    <t>3387212487</t>
-  </si>
-  <si>
-    <t>franz.bottoni@alice.it</t>
-  </si>
-  <si>
-    <t>BTTFNC57H11H501O</t>
-  </si>
-  <si>
-    <t>U151P0700F</t>
-  </si>
-  <si>
-    <t>MIT-UCO</t>
-  </si>
-  <si>
-    <t>FIORE</t>
-  </si>
-  <si>
-    <t>VIALE ALDO BALLARIN 138</t>
-  </si>
-  <si>
-    <t>3471936906</t>
-  </si>
-  <si>
-    <t>pfiore1009@gmail.com</t>
-  </si>
-  <si>
-    <t>FRIPLA65P50H501N</t>
-  </si>
-  <si>
-    <t>U178Z1418X</t>
-  </si>
-  <si>
-    <t>GRUOSSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FABIO </t>
-  </si>
-  <si>
-    <t>VIA SALVO RANDONE</t>
-  </si>
-  <si>
-    <t>3335268050</t>
-  </si>
-  <si>
-    <t>ciccioni_2007@libero.it</t>
-  </si>
-  <si>
-    <t>GRSFBA83D29H501R</t>
-  </si>
-  <si>
-    <t>CA50195EX</t>
-  </si>
-  <si>
-    <t>MINISTERO INTERNO</t>
-  </si>
-  <si>
-    <t>PALLINI</t>
-  </si>
-  <si>
-    <t>VIA VECCHIA DI POZZOLATICO 17</t>
-  </si>
-  <si>
-    <t>3332753430</t>
-  </si>
-  <si>
-    <t>robertopallini2@gmail.com</t>
-  </si>
-  <si>
-    <t>PLLRRT55L25D612T</t>
-  </si>
-  <si>
-    <t>CA70380IT</t>
-  </si>
-  <si>
-    <t>COMUNE DI FIRENZE</t>
-  </si>
-  <si>
-    <t>INTOLLERANZA AGLIO</t>
-  </si>
-  <si>
-    <t>GIARRE'</t>
-  </si>
-  <si>
-    <t>GIOVANNA</t>
-  </si>
-  <si>
-    <t>3388812477</t>
-  </si>
-  <si>
-    <t>giovanna.giarre@gmail.com</t>
-  </si>
-  <si>
-    <t>GRRGNN57D65G843F</t>
-  </si>
-  <si>
-    <t>CA95518TC</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>VIA CASTELLO 12</t>
-  </si>
-  <si>
-    <t>3932666173</t>
-  </si>
-  <si>
-    <t>omar.belotti73@gmail.com</t>
-  </si>
-  <si>
-    <t>BLTMRO73M07H910O</t>
-  </si>
-  <si>
-    <t>CA36105WL</t>
-  </si>
-  <si>
-    <t>PREITE</t>
-  </si>
-  <si>
-    <t>MARCO GIACOMO</t>
-  </si>
-  <si>
-    <t>VIA DANTE ALIGHIERI 27</t>
-  </si>
-  <si>
-    <t>3931231234</t>
-  </si>
-  <si>
-    <t>eletraessere_srl@yahoo.it</t>
-  </si>
-  <si>
-    <t>PRTMCG72T15H910E</t>
-  </si>
-  <si>
-    <t>CA83782IN</t>
-  </si>
-  <si>
-    <t>COMUNE ALMENNO SAN BARTOLOMEO</t>
-  </si>
-  <si>
-    <t>POLLINI</t>
-  </si>
-  <si>
-    <t>VIA BEATO NICONE N.13</t>
-  </si>
-  <si>
-    <t>3396588988</t>
-  </si>
-  <si>
-    <t>asmpollini@libero.it</t>
-  </si>
-  <si>
-    <t>PLLMRC59C16F205C</t>
-  </si>
-  <si>
-    <t>AZ0928893</t>
-  </si>
-  <si>
-    <t>BESOZZO</t>
-  </si>
-  <si>
-    <t>DI GIROLAMO</t>
-  </si>
-  <si>
-    <t>3442948830</t>
-  </si>
-  <si>
-    <t>info@limotaximilano.com</t>
-  </si>
-  <si>
-    <t>DGRSRG70H14I819Q</t>
-  </si>
-  <si>
-    <t>CA79235AP</t>
-  </si>
-  <si>
-    <t>CASSANO MAGNAGO</t>
-  </si>
-  <si>
-    <t>MOSTARDA</t>
-  </si>
-  <si>
-    <t>VIA ROMA 46</t>
-  </si>
-  <si>
-    <t>3892717592</t>
-  </si>
-  <si>
-    <t>claudiomostarda@gmail.com</t>
-  </si>
-  <si>
-    <t>MSTCLD63E14H501M</t>
-  </si>
-  <si>
-    <t>CA702806QH</t>
-  </si>
-  <si>
-    <t>RIVODUTRI</t>
-  </si>
-  <si>
-    <t>MARIANI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIANLUIGI </t>
-  </si>
-  <si>
-    <t>3248608126</t>
-  </si>
-  <si>
-    <t>gianluigimariani89@libero.it</t>
-  </si>
-  <si>
-    <t>MRNGLG89R27F839S</t>
-  </si>
-  <si>
-    <t>CA16303HF</t>
-  </si>
-  <si>
-    <t>COMUNE CUNEO</t>
-  </si>
-  <si>
-    <t>NULLA</t>
-  </si>
-  <si>
-    <t>CROCIANI</t>
-  </si>
-  <si>
-    <t>VIA BARTOLOMEO VANZETTI 15</t>
-  </si>
-  <si>
-    <t>3285966715</t>
-  </si>
-  <si>
-    <t>matteocrociani2@gmail.com</t>
-  </si>
-  <si>
-    <t>CRCMTT83H15D704Y</t>
-  </si>
-  <si>
-    <t>CA57525QV</t>
-  </si>
-  <si>
-    <t>COMUNE DI FORLI'</t>
-  </si>
-  <si>
-    <t>BONAFE'</t>
-  </si>
-  <si>
-    <t>39349784058</t>
-  </si>
-  <si>
-    <t>benedetta.bonafe@gmail.com</t>
-  </si>
-  <si>
-    <t>BNFBXX88B66E379G</t>
-  </si>
-  <si>
-    <t>CA30471FS</t>
-  </si>
-  <si>
-    <t>COMUNE DI IVREA</t>
-  </si>
-  <si>
-    <t>DI VINCENZO</t>
-  </si>
-  <si>
-    <t>MARIA ENZA</t>
-  </si>
-  <si>
-    <t>3393729169</t>
-  </si>
-  <si>
-    <t>mari.divincenzo@gmail.com</t>
-  </si>
-  <si>
-    <t>DVNMNZ68L57A479J</t>
-  </si>
-  <si>
-    <t>4614584AA</t>
-  </si>
-  <si>
-    <t>SCARLASSARE</t>
-  </si>
-  <si>
-    <t>3351360543</t>
-  </si>
-  <si>
-    <t>laurascarlassare66@gmail.com</t>
-  </si>
-  <si>
-    <t>SCRLRA66M41I531E</t>
-  </si>
-  <si>
-    <t>CA79722HN</t>
-  </si>
-  <si>
-    <t>GELFI</t>
-  </si>
-  <si>
-    <t>mauriziogelfi@hotmail.it</t>
-  </si>
-  <si>
-    <t>U15V19957N</t>
-  </si>
-  <si>
-    <t>MIMOUNE</t>
-  </si>
-  <si>
-    <t>NACIRI</t>
-  </si>
-  <si>
-    <t>VIA ALESSANDRO VOLTA, 1</t>
-  </si>
-  <si>
-    <t>35192681</t>
-  </si>
-  <si>
-    <t>nacirimimoune9@gmail.com</t>
-  </si>
-  <si>
-    <t>NCRMMN06T09Z330V</t>
-  </si>
-  <si>
-    <t>CA81582RN</t>
   </si>
   <si>
     <t>VIA VODICE 9</t>
@@ -51129,36 +51138,44 @@
     </row>
     <row r="601" customHeight="1" ht="20">
       <c r="A601" s="5" t="n">
-        <v>3305</v>
+        <v>3943</v>
       </c>
       <c r="B601" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C601" s="6" t="s">
-        <v>1400</v>
+        <v>2167</v>
       </c>
       <c r="D601" s="6" t="s">
-        <v>168</v>
+        <v>2168</v>
       </c>
       <c r="E601" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F601" s="5" t="n">
-        <v>71439</v>
-      </c>
-      <c r="G601" s="6"/>
+        <v>71919</v>
+      </c>
+      <c r="G601" s="6" t="s">
+        <v>2169</v>
+      </c>
       <c r="H601" s="5" t="n">
-        <v>72597</v>
+        <v>76170</v>
       </c>
       <c r="I601" s="7" t="n">
-        <v>38995</v>
-      </c>
-      <c r="J601" s="6"/>
-      <c r="K601" s="6"/>
+        <v>31507</v>
+      </c>
+      <c r="J601" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="K601" s="6" t="s">
+        <v>2170</v>
+      </c>
       <c r="L601" s="6" t="s">
-        <v>2167</v>
-      </c>
-      <c r="M601" s="6"/>
+        <v>2171</v>
+      </c>
+      <c r="M601" s="6" t="s">
+        <v>2172</v>
+      </c>
       <c r="N601" s="6"/>
       <c r="O601" s="6" t="s">
         <v>44</v>
@@ -51170,16 +51187,16 @@
         <v>66</v>
       </c>
       <c r="R601" s="6" t="s">
-        <v>2168</v>
+        <v>2173</v>
       </c>
       <c r="S601" s="6" t="s">
-        <v>2169</v>
+        <v>2174</v>
       </c>
       <c r="T601" s="7" t="n">
-        <v>45600</v>
+        <v>43532</v>
       </c>
       <c r="U601" s="7" t="n">
-        <v>49222</v>
+        <v>47213</v>
       </c>
       <c r="V601" s="6"/>
       <c r="W601" s="6"/>
@@ -51191,49 +51208,45 @@
       <c r="AC601" s="6"/>
       <c r="AD601" s="7"/>
       <c r="AE601" s="6" t="s">
-        <v>1104</v>
+        <v>51</v>
       </c>
       <c r="AF601" s="8" t="n">
-        <v>45812.3288888889</v>
-      </c>
-      <c r="AG601" s="6" t="s">
-        <v>1259</v>
-      </c>
-      <c r="AH601" s="8" t="n">
-        <v>45831.8282060185</v>
-      </c>
+        <v>46042.2900115741</v>
+      </c>
+      <c r="AG601" s="6"/>
+      <c r="AH601" s="8"/>
       <c r="AI601" s="6"/>
     </row>
     <row r="602" customHeight="1" ht="20">
       <c r="A602" s="5" t="n">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="B602" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C602" s="6" t="s">
-        <v>2170</v>
+        <v>1400</v>
       </c>
       <c r="D602" s="6" t="s">
-        <v>302</v>
+        <v>168</v>
       </c>
       <c r="E602" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F602" s="5" t="n">
-        <v>69863</v>
+        <v>71439</v>
       </c>
       <c r="G602" s="6"/>
       <c r="H602" s="5" t="n">
-        <v>76070</v>
+        <v>72597</v>
       </c>
       <c r="I602" s="7" t="n">
-        <v>24288</v>
+        <v>38995</v>
       </c>
       <c r="J602" s="6"/>
       <c r="K602" s="6"/>
       <c r="L602" s="6" t="s">
-        <v>2171</v>
+        <v>2175</v>
       </c>
       <c r="M602" s="6"/>
       <c r="N602" s="6"/>
@@ -51244,19 +51257,19 @@
         <v>44</v>
       </c>
       <c r="Q602" s="6" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="R602" s="6" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="S602" s="6" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="T602" s="7" t="n">
-        <v>42361</v>
+        <v>45600</v>
       </c>
       <c r="U602" s="7" t="n">
-        <v>46013</v>
+        <v>49222</v>
       </c>
       <c r="V602" s="6"/>
       <c r="W602" s="6"/>
@@ -51271,7 +51284,7 @@
         <v>1104</v>
       </c>
       <c r="AF602" s="8" t="n">
-        <v>45812</v>
+        <v>45812.3288888889</v>
       </c>
       <c r="AG602" s="6" t="s">
         <v>1259</v>
@@ -51283,40 +51296,34 @@
     </row>
     <row r="603" customHeight="1" ht="20">
       <c r="A603" s="5" t="n">
-        <v>3326</v>
+        <v>3306</v>
       </c>
       <c r="B603" s="6" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C603" s="6" t="s">
-        <v>2174</v>
+        <v>2178</v>
       </c>
       <c r="D603" s="6" t="s">
-        <v>55</v>
+        <v>302</v>
       </c>
       <c r="E603" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F603" s="5" t="n">
-        <v>69720</v>
-      </c>
-      <c r="G603" s="6" t="s">
-        <v>2175</v>
-      </c>
+        <v>69863</v>
+      </c>
+      <c r="G603" s="6"/>
       <c r="H603" s="5" t="n">
-        <v>76091</v>
+        <v>76070</v>
       </c>
       <c r="I603" s="7" t="n">
-        <v>22100</v>
-      </c>
-      <c r="J603" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K603" s="6" t="s">
-        <v>2176</v>
-      </c>
+        <v>24288</v>
+      </c>
+      <c r="J603" s="6"/>
+      <c r="K603" s="6"/>
       <c r="L603" s="6" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="M603" s="6"/>
       <c r="N603" s="6"/>
@@ -51327,19 +51334,19 @@
         <v>44</v>
       </c>
       <c r="Q603" s="6" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="R603" s="6" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="S603" s="6" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="T603" s="7" t="n">
-        <v>42761</v>
+        <v>42361</v>
       </c>
       <c r="U603" s="7" t="n">
-        <v>46571</v>
+        <v>46013</v>
       </c>
       <c r="V603" s="6"/>
       <c r="W603" s="6"/>
@@ -51354,7 +51361,7 @@
         <v>1104</v>
       </c>
       <c r="AF603" s="8" t="n">
-        <v>45816</v>
+        <v>45812</v>
       </c>
       <c r="AG603" s="6" t="s">
         <v>1259</v>
@@ -51366,40 +51373,40 @@
     </row>
     <row r="604" customHeight="1" ht="20">
       <c r="A604" s="5" t="n">
-        <v>3372</v>
+        <v>3326</v>
       </c>
       <c r="B604" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C604" s="6" t="s">
-        <v>2152</v>
+        <v>2182</v>
       </c>
       <c r="D604" s="6" t="s">
-        <v>676</v>
+        <v>55</v>
       </c>
       <c r="E604" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F604" s="5" t="n">
-        <v>69863</v>
+        <v>69720</v>
       </c>
       <c r="G604" s="6" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H604" s="5" t="n">
-        <v>69863</v>
+        <v>76091</v>
       </c>
       <c r="I604" s="7" t="n">
-        <v>29221</v>
+        <v>22100</v>
       </c>
       <c r="J604" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K604" s="6" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="L604" s="6" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="M604" s="6"/>
       <c r="N604" s="6"/>
@@ -51413,16 +51420,16 @@
         <v>66</v>
       </c>
       <c r="R604" s="6" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="S604" s="6" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="T604" s="7" t="n">
-        <v>43831</v>
+        <v>42761</v>
       </c>
       <c r="U604" s="7" t="n">
-        <v>47484</v>
+        <v>46571</v>
       </c>
       <c r="V604" s="6"/>
       <c r="W604" s="6"/>
@@ -51434,55 +51441,57 @@
       <c r="AC604" s="6"/>
       <c r="AD604" s="7"/>
       <c r="AE604" s="6" t="s">
-        <v>51</v>
+        <v>1104</v>
       </c>
       <c r="AF604" s="8" t="n">
-        <v>45832.3930092593</v>
-      </c>
-      <c r="AG604" s="6"/>
-      <c r="AH604" s="8"/>
+        <v>45816</v>
+      </c>
+      <c r="AG604" s="6" t="s">
+        <v>1259</v>
+      </c>
+      <c r="AH604" s="8" t="n">
+        <v>45831.8282060185</v>
+      </c>
       <c r="AI604" s="6"/>
     </row>
     <row r="605" customHeight="1" ht="20">
       <c r="A605" s="5" t="n">
-        <v>3464</v>
+        <v>3372</v>
       </c>
       <c r="B605" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C605" s="6" t="s">
-        <v>2185</v>
+        <v>2152</v>
       </c>
       <c r="D605" s="6" t="s">
-        <v>2186</v>
+        <v>676</v>
       </c>
       <c r="E605" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F605" s="5" t="n">
-        <v>73084</v>
+        <v>69863</v>
       </c>
       <c r="G605" s="6" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="H605" s="5" t="n">
-        <v>73084</v>
+        <v>69863</v>
       </c>
       <c r="I605" s="7" t="n">
-        <v>22765</v>
+        <v>29221</v>
       </c>
       <c r="J605" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K605" s="6" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="L605" s="6" t="s">
-        <v>2189</v>
-      </c>
-      <c r="M605" s="6" t="s">
         <v>2190</v>
       </c>
+      <c r="M605" s="6"/>
       <c r="N605" s="6"/>
       <c r="O605" s="6" t="s">
         <v>44</v>
@@ -51496,12 +51505,14 @@
       <c r="R605" s="6" t="s">
         <v>2191</v>
       </c>
-      <c r="S605" s="6"/>
+      <c r="S605" s="6" t="s">
+        <v>2192</v>
+      </c>
       <c r="T605" s="7" t="n">
-        <v>45856</v>
+        <v>43831</v>
       </c>
       <c r="U605" s="7" t="n">
-        <v>49428</v>
+        <v>47484</v>
       </c>
       <c r="V605" s="6"/>
       <c r="W605" s="6"/>
@@ -51513,10 +51524,10 @@
       <c r="AC605" s="6"/>
       <c r="AD605" s="7"/>
       <c r="AE605" s="6" t="s">
-        <v>1104</v>
+        <v>51</v>
       </c>
       <c r="AF605" s="8" t="n">
-        <v>45895.631724537</v>
+        <v>45832.3930092593</v>
       </c>
       <c r="AG605" s="6"/>
       <c r="AH605" s="8"/>
@@ -51524,43 +51535,43 @@
     </row>
     <row r="606" customHeight="1" ht="20">
       <c r="A606" s="5" t="n">
-        <v>3483</v>
+        <v>3464</v>
       </c>
       <c r="B606" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C606" s="6" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="D606" s="6" t="s">
-        <v>764</v>
+        <v>2194</v>
       </c>
       <c r="E606" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F606" s="5" t="n">
-        <v>69437</v>
+        <v>73084</v>
       </c>
       <c r="G606" s="6" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="H606" s="5" t="n">
-        <v>68588</v>
+        <v>73084</v>
       </c>
       <c r="I606" s="7" t="n">
-        <v>25816</v>
+        <v>22765</v>
       </c>
       <c r="J606" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K606" s="6" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="L606" s="6" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="M606" s="6" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="N606" s="6"/>
       <c r="O606" s="6" t="s">
@@ -51573,16 +51584,14 @@
         <v>66</v>
       </c>
       <c r="R606" s="6" t="s">
-        <v>2197</v>
-      </c>
-      <c r="S606" s="6" t="s">
-        <v>2198</v>
-      </c>
+        <v>2199</v>
+      </c>
+      <c r="S606" s="6"/>
       <c r="T606" s="7" t="n">
-        <v>45307</v>
+        <v>45856</v>
       </c>
       <c r="U606" s="7" t="n">
-        <v>48827</v>
+        <v>49428</v>
       </c>
       <c r="V606" s="6"/>
       <c r="W606" s="6"/>
@@ -51597,41 +51606,39 @@
         <v>1104</v>
       </c>
       <c r="AF606" s="8" t="n">
-        <v>45903.5703587963</v>
+        <v>45895.631724537</v>
       </c>
       <c r="AG606" s="6"/>
       <c r="AH606" s="8"/>
-      <c r="AI606" s="6" t="s">
-        <v>2199</v>
-      </c>
+      <c r="AI606" s="6"/>
     </row>
     <row r="607" customHeight="1" ht="20">
       <c r="A607" s="5" t="n">
-        <v>3664</v>
+        <v>3483</v>
       </c>
       <c r="B607" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C607" s="6" t="s">
         <v>2200</v>
       </c>
       <c r="D607" s="6" t="s">
-        <v>1261</v>
+        <v>764</v>
       </c>
       <c r="E607" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F607" s="5" t="n">
-        <v>73084</v>
+        <v>69437</v>
       </c>
       <c r="G607" s="6" t="s">
         <v>2201</v>
       </c>
       <c r="H607" s="5" t="n">
-        <v>73084</v>
+        <v>68588</v>
       </c>
       <c r="I607" s="7" t="n">
-        <v>24669</v>
+        <v>25816</v>
       </c>
       <c r="J607" s="6" t="s">
         <v>40</v>
@@ -51642,7 +51649,9 @@
       <c r="L607" s="6" t="s">
         <v>2203</v>
       </c>
-      <c r="M607" s="6"/>
+      <c r="M607" s="6" t="s">
+        <v>2204</v>
+      </c>
       <c r="N607" s="6"/>
       <c r="O607" s="6" t="s">
         <v>44</v>
@@ -51654,16 +51663,16 @@
         <v>66</v>
       </c>
       <c r="R607" s="6" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="S607" s="6" t="s">
-        <v>1391</v>
+        <v>2206</v>
       </c>
       <c r="T607" s="7" t="n">
-        <v>45798</v>
+        <v>45307</v>
       </c>
       <c r="U607" s="7" t="n">
-        <v>49141</v>
+        <v>48827</v>
       </c>
       <c r="V607" s="6"/>
       <c r="W607" s="6"/>
@@ -51678,52 +51687,52 @@
         <v>1104</v>
       </c>
       <c r="AF607" s="8" t="n">
-        <v>45964.6296990741</v>
+        <v>45903.5703587963</v>
       </c>
       <c r="AG607" s="6"/>
       <c r="AH607" s="8"/>
-      <c r="AI607" s="6"/>
+      <c r="AI607" s="6" t="s">
+        <v>2207</v>
+      </c>
     </row>
     <row r="608" customHeight="1" ht="20">
       <c r="A608" s="5" t="n">
-        <v>3670</v>
+        <v>3664</v>
       </c>
       <c r="B608" s="6" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C608" s="6" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="D608" s="6" t="s">
-        <v>1360</v>
+        <v>1261</v>
       </c>
       <c r="E608" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F608" s="5" t="n">
-        <v>72731</v>
+        <v>73084</v>
       </c>
       <c r="G608" s="6" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="H608" s="5" t="n">
-        <v>73166</v>
+        <v>73084</v>
       </c>
       <c r="I608" s="7" t="n">
-        <v>23467</v>
+        <v>24669</v>
       </c>
       <c r="J608" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K608" s="6" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="L608" s="6" t="s">
-        <v>2208</v>
-      </c>
-      <c r="M608" s="6" t="s">
-        <v>2209</v>
-      </c>
+        <v>2211</v>
+      </c>
+      <c r="M608" s="6"/>
       <c r="N608" s="6"/>
       <c r="O608" s="6" t="s">
         <v>44</v>
@@ -51735,16 +51744,16 @@
         <v>66</v>
       </c>
       <c r="R608" s="6" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="S608" s="6" t="s">
-        <v>2211</v>
+        <v>1391</v>
       </c>
       <c r="T608" s="7" t="n">
-        <v>44442</v>
+        <v>45798</v>
       </c>
       <c r="U608" s="7" t="n">
-        <v>48304</v>
+        <v>49141</v>
       </c>
       <c r="V608" s="6"/>
       <c r="W608" s="6"/>
@@ -51759,7 +51768,7 @@
         <v>1104</v>
       </c>
       <c r="AF608" s="8" t="n">
-        <v>45966.446400463</v>
+        <v>45964.6296990741</v>
       </c>
       <c r="AG608" s="6"/>
       <c r="AH608" s="8"/>
@@ -51767,43 +51776,43 @@
     </row>
     <row r="609" customHeight="1" ht="20">
       <c r="A609" s="5" t="n">
-        <v>3675</v>
+        <v>3670</v>
       </c>
       <c r="B609" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C609" s="6" t="s">
-        <v>995</v>
+        <v>2213</v>
       </c>
       <c r="D609" s="6" t="s">
-        <v>750</v>
+        <v>1360</v>
       </c>
       <c r="E609" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F609" s="5" t="n">
-        <v>67226</v>
+        <v>72731</v>
       </c>
       <c r="G609" s="6" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="H609" s="5" t="n">
-        <v>67756</v>
+        <v>73166</v>
       </c>
       <c r="I609" s="7" t="n">
-        <v>25807</v>
+        <v>23467</v>
       </c>
       <c r="J609" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K609" s="6" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="L609" s="6" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="M609" s="6" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="N609" s="6"/>
       <c r="O609" s="6" t="s">
@@ -51816,16 +51825,16 @@
         <v>66</v>
       </c>
       <c r="R609" s="6" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="S609" s="6" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="T609" s="7" t="n">
-        <v>44705</v>
+        <v>44442</v>
       </c>
       <c r="U609" s="7" t="n">
-        <v>48453</v>
+        <v>48304</v>
       </c>
       <c r="V609" s="6"/>
       <c r="W609" s="6"/>
@@ -51840,7 +51849,7 @@
         <v>1104</v>
       </c>
       <c r="AF609" s="8" t="n">
-        <v>45967.322962963</v>
+        <v>45966.446400463</v>
       </c>
       <c r="AG609" s="6"/>
       <c r="AH609" s="8"/>
@@ -51848,31 +51857,31 @@
     </row>
     <row r="610" customHeight="1" ht="20">
       <c r="A610" s="5" t="n">
-        <v>3684</v>
+        <v>3675</v>
       </c>
       <c r="B610" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C610" s="6" t="s">
-        <v>2218</v>
+        <v>995</v>
       </c>
       <c r="D610" s="6" t="s">
-        <v>2219</v>
+        <v>750</v>
       </c>
       <c r="E610" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F610" s="5" t="n">
-        <v>67348</v>
+        <v>67226</v>
       </c>
       <c r="G610" s="6" t="s">
         <v>2220</v>
       </c>
       <c r="H610" s="5" t="n">
-        <v>67348</v>
+        <v>67756</v>
       </c>
       <c r="I610" s="7" t="n">
-        <v>24866</v>
+        <v>25807</v>
       </c>
       <c r="J610" s="6" t="s">
         <v>40</v>
@@ -51903,10 +51912,10 @@
         <v>2225</v>
       </c>
       <c r="T610" s="7" t="n">
-        <v>44754</v>
+        <v>44705</v>
       </c>
       <c r="U610" s="7" t="n">
-        <v>48608</v>
+        <v>48453</v>
       </c>
       <c r="V610" s="6"/>
       <c r="W610" s="6"/>
@@ -51921,7 +51930,7 @@
         <v>1104</v>
       </c>
       <c r="AF610" s="8" t="n">
-        <v>45977.6644444444</v>
+        <v>45967.322962963</v>
       </c>
       <c r="AG610" s="6"/>
       <c r="AH610" s="8"/>
@@ -51929,43 +51938,43 @@
     </row>
     <row r="611" customHeight="1" ht="20">
       <c r="A611" s="5" t="n">
-        <v>3705</v>
+        <v>3684</v>
       </c>
       <c r="B611" s="6" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C611" s="6" t="s">
         <v>2226</v>
       </c>
       <c r="D611" s="6" t="s">
-        <v>168</v>
+        <v>2227</v>
       </c>
       <c r="E611" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F611" s="5" t="n">
-        <v>69952</v>
+        <v>67348</v>
       </c>
       <c r="G611" s="6" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="H611" s="5" t="n">
-        <v>66179</v>
+        <v>67348</v>
       </c>
       <c r="I611" s="7" t="n">
-        <v>25577</v>
+        <v>24866</v>
       </c>
       <c r="J611" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K611" s="6" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="L611" s="6" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="M611" s="6" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="N611" s="6"/>
       <c r="O611" s="6" t="s">
@@ -51978,16 +51987,16 @@
         <v>66</v>
       </c>
       <c r="R611" s="6" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="S611" s="6" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="T611" s="7" t="n">
-        <v>44616</v>
+        <v>44754</v>
       </c>
       <c r="U611" s="7" t="n">
-        <v>48588</v>
+        <v>48608</v>
       </c>
       <c r="V611" s="6"/>
       <c r="W611" s="6"/>
@@ -52002,7 +52011,7 @@
         <v>1104</v>
       </c>
       <c r="AF611" s="8" t="n">
-        <v>45982.377349537</v>
+        <v>45977.6644444444</v>
       </c>
       <c r="AG611" s="6"/>
       <c r="AH611" s="8"/>
@@ -52010,31 +52019,31 @@
     </row>
     <row r="612" customHeight="1" ht="20">
       <c r="A612" s="5" t="n">
-        <v>3732</v>
+        <v>3705</v>
       </c>
       <c r="B612" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C612" s="6" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="D612" s="6" t="s">
-        <v>2234</v>
+        <v>168</v>
       </c>
       <c r="E612" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F612" s="5" t="n">
-        <v>71329</v>
+        <v>69952</v>
       </c>
       <c r="G612" s="6" t="s">
         <v>2235</v>
       </c>
       <c r="H612" s="5" t="n">
-        <v>66208</v>
+        <v>66179</v>
       </c>
       <c r="I612" s="7" t="n">
-        <v>33378</v>
+        <v>25577</v>
       </c>
       <c r="J612" s="6" t="s">
         <v>40</v>
@@ -52045,7 +52054,9 @@
       <c r="L612" s="6" t="s">
         <v>2237</v>
       </c>
-      <c r="M612" s="6"/>
+      <c r="M612" s="6" t="s">
+        <v>2238</v>
+      </c>
       <c r="N612" s="6"/>
       <c r="O612" s="6" t="s">
         <v>44</v>
@@ -52057,16 +52068,16 @@
         <v>66</v>
       </c>
       <c r="R612" s="6" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="S612" s="6" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="T612" s="7" t="n">
-        <v>42770</v>
+        <v>44616</v>
       </c>
       <c r="U612" s="7" t="n">
-        <v>46527</v>
+        <v>48588</v>
       </c>
       <c r="V612" s="6"/>
       <c r="W612" s="6"/>
@@ -52081,58 +52092,50 @@
         <v>1104</v>
       </c>
       <c r="AF612" s="8" t="n">
-        <v>45985.7474305556</v>
-      </c>
-      <c r="AG612" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH612" s="8" t="n">
-        <v>45985.747662037</v>
-      </c>
-      <c r="AI612" s="6" t="s">
-        <v>2240</v>
-      </c>
+        <v>45982.377349537</v>
+      </c>
+      <c r="AG612" s="6"/>
+      <c r="AH612" s="8"/>
+      <c r="AI612" s="6"/>
     </row>
     <row r="613" customHeight="1" ht="20">
       <c r="A613" s="5" t="n">
-        <v>3743</v>
+        <v>3732</v>
       </c>
       <c r="B613" s="6" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C613" s="6" t="s">
-        <v>2001</v>
+        <v>2241</v>
       </c>
       <c r="D613" s="6" t="s">
-        <v>524</v>
+        <v>2242</v>
       </c>
       <c r="E613" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F613" s="5" t="n">
-        <v>66179</v>
+        <v>71329</v>
       </c>
       <c r="G613" s="6" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="H613" s="5" t="n">
-        <v>66179</v>
+        <v>66208</v>
       </c>
       <c r="I613" s="7" t="n">
-        <v>24040</v>
+        <v>33378</v>
       </c>
       <c r="J613" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K613" s="6" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="L613" s="6" t="s">
-        <v>2243</v>
-      </c>
-      <c r="M613" s="6" t="s">
-        <v>2244</v>
-      </c>
+        <v>2245</v>
+      </c>
+      <c r="M613" s="6"/>
       <c r="N613" s="6"/>
       <c r="O613" s="6" t="s">
         <v>44</v>
@@ -52144,16 +52147,16 @@
         <v>66</v>
       </c>
       <c r="R613" s="6" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="S613" s="6" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="T613" s="7" t="n">
-        <v>44845</v>
+        <v>42770</v>
       </c>
       <c r="U613" s="7" t="n">
-        <v>48146</v>
+        <v>46527</v>
       </c>
       <c r="V613" s="6"/>
       <c r="W613" s="6"/>
@@ -52168,51 +52171,57 @@
         <v>1104</v>
       </c>
       <c r="AF613" s="8" t="n">
-        <v>45989.3553356481</v>
-      </c>
-      <c r="AG613" s="6"/>
-      <c r="AH613" s="8"/>
-      <c r="AI613" s="6"/>
+        <v>45985.7474305556</v>
+      </c>
+      <c r="AG613" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH613" s="8" t="n">
+        <v>45985.747662037</v>
+      </c>
+      <c r="AI613" s="6" t="s">
+        <v>2248</v>
+      </c>
     </row>
     <row r="614" customHeight="1" ht="20">
       <c r="A614" s="5" t="n">
-        <v>3763</v>
+        <v>3743</v>
       </c>
       <c r="B614" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C614" s="6" t="s">
-        <v>2247</v>
+        <v>2001</v>
       </c>
       <c r="D614" s="6" t="s">
-        <v>168</v>
+        <v>524</v>
       </c>
       <c r="E614" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F614" s="5" t="n">
-        <v>72518</v>
+        <v>66179</v>
       </c>
       <c r="G614" s="6" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="H614" s="5" t="n">
-        <v>72518</v>
+        <v>66179</v>
       </c>
       <c r="I614" s="7" t="n">
-        <v>23460</v>
+        <v>24040</v>
       </c>
       <c r="J614" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K614" s="6" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="L614" s="6" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="M614" s="6" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="N614" s="6"/>
       <c r="O614" s="6" t="s">
@@ -52225,16 +52234,16 @@
         <v>66</v>
       </c>
       <c r="R614" s="6" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="S614" s="6" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="T614" s="7" t="n">
-        <v>44140</v>
+        <v>44845</v>
       </c>
       <c r="U614" s="7" t="n">
-        <v>47931</v>
+        <v>48146</v>
       </c>
       <c r="V614" s="6"/>
       <c r="W614" s="6"/>
@@ -52249,7 +52258,7 @@
         <v>1104</v>
       </c>
       <c r="AF614" s="8" t="n">
-        <v>45992.5116435185</v>
+        <v>45989.3553356481</v>
       </c>
       <c r="AG614" s="6"/>
       <c r="AH614" s="8"/>
@@ -52257,43 +52266,43 @@
     </row>
     <row r="615" customHeight="1" ht="20">
       <c r="A615" s="5" t="n">
-        <v>3818</v>
+        <v>3763</v>
       </c>
       <c r="B615" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C615" s="6" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="D615" s="6" t="s">
-        <v>2099</v>
+        <v>168</v>
       </c>
       <c r="E615" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F615" s="5" t="n">
-        <v>71300</v>
+        <v>72518</v>
       </c>
       <c r="G615" s="6" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="H615" s="5" t="n">
-        <v>65894</v>
+        <v>72518</v>
       </c>
       <c r="I615" s="7" t="n">
-        <v>35240</v>
+        <v>23460</v>
       </c>
       <c r="J615" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K615" s="6" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="L615" s="6" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="M615" s="6" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="N615" s="6"/>
       <c r="O615" s="6" t="s">
@@ -52303,19 +52312,19 @@
         <v>44</v>
       </c>
       <c r="Q615" s="6" t="s">
-        <v>469</v>
+        <v>66</v>
       </c>
       <c r="R615" s="6" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="S615" s="6" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="T615" s="7" t="n">
-        <v>44440</v>
+        <v>44140</v>
       </c>
       <c r="U615" s="7" t="n">
-        <v>48389</v>
+        <v>47931</v>
       </c>
       <c r="V615" s="6"/>
       <c r="W615" s="6"/>
@@ -52330,7 +52339,7 @@
         <v>1104</v>
       </c>
       <c r="AF615" s="8" t="n">
-        <v>46002.8828356481</v>
+        <v>45992.5116435185</v>
       </c>
       <c r="AG615" s="6"/>
       <c r="AH615" s="8"/>
@@ -52338,36 +52347,44 @@
     </row>
     <row r="616" customHeight="1" ht="20">
       <c r="A616" s="5" t="n">
-        <v>3327</v>
+        <v>3818</v>
       </c>
       <c r="B616" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C616" s="6" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="D616" s="6" t="s">
-        <v>302</v>
+        <v>2099</v>
       </c>
       <c r="E616" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F616" s="5" t="n">
-        <v>69720</v>
+        <v>71300</v>
       </c>
       <c r="G616" s="6" t="s">
-        <v>2175</v>
+        <v>2263</v>
       </c>
       <c r="H616" s="5" t="n">
-        <v>72707</v>
+        <v>65894</v>
       </c>
       <c r="I616" s="7" t="n">
-        <v>22508</v>
-      </c>
-      <c r="J616" s="6"/>
-      <c r="K616" s="6"/>
-      <c r="L616" s="6"/>
-      <c r="M616" s="6"/>
+        <v>35240</v>
+      </c>
+      <c r="J616" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K616" s="6" t="s">
+        <v>2264</v>
+      </c>
+      <c r="L616" s="6" t="s">
+        <v>2265</v>
+      </c>
+      <c r="M616" s="6" t="s">
+        <v>2266</v>
+      </c>
       <c r="N616" s="6"/>
       <c r="O616" s="6" t="s">
         <v>44</v>
@@ -52376,19 +52393,19 @@
         <v>44</v>
       </c>
       <c r="Q616" s="6" t="s">
-        <v>66</v>
+        <v>469</v>
       </c>
       <c r="R616" s="6" t="s">
-        <v>2262</v>
+        <v>2267</v>
       </c>
       <c r="S616" s="6" t="s">
-        <v>2179</v>
+        <v>2268</v>
       </c>
       <c r="T616" s="7" t="n">
-        <v>42761</v>
+        <v>44440</v>
       </c>
       <c r="U616" s="7" t="n">
-        <v>46614</v>
+        <v>48389</v>
       </c>
       <c r="V616" s="6"/>
       <c r="W616" s="6"/>
@@ -52403,56 +52420,44 @@
         <v>1104</v>
       </c>
       <c r="AF616" s="8" t="n">
-        <v>45816.6759837963</v>
-      </c>
-      <c r="AG616" s="6" t="s">
-        <v>1259</v>
-      </c>
-      <c r="AH616" s="8" t="n">
-        <v>45831.8282060185</v>
-      </c>
+        <v>46002.8828356481</v>
+      </c>
+      <c r="AG616" s="6"/>
+      <c r="AH616" s="8"/>
       <c r="AI616" s="6"/>
     </row>
     <row r="617" customHeight="1" ht="20">
       <c r="A617" s="5" t="n">
-        <v>3503</v>
+        <v>3327</v>
       </c>
       <c r="B617" s="6" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C617" s="6" t="s">
-        <v>2263</v>
+        <v>2269</v>
       </c>
       <c r="D617" s="6" t="s">
-        <v>113</v>
+        <v>302</v>
       </c>
       <c r="E617" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F617" s="5" t="n">
-        <v>72223</v>
+        <v>69720</v>
       </c>
       <c r="G617" s="6" t="s">
-        <v>2264</v>
+        <v>2183</v>
       </c>
       <c r="H617" s="5" t="n">
-        <v>68588</v>
+        <v>72707</v>
       </c>
       <c r="I617" s="7" t="n">
-        <v>23611</v>
-      </c>
-      <c r="J617" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K617" s="6" t="s">
-        <v>2265</v>
-      </c>
-      <c r="L617" s="6" t="s">
-        <v>2266</v>
-      </c>
-      <c r="M617" s="6" t="s">
-        <v>2267</v>
-      </c>
+        <v>22508</v>
+      </c>
+      <c r="J617" s="6"/>
+      <c r="K617" s="6"/>
+      <c r="L617" s="6"/>
+      <c r="M617" s="6"/>
       <c r="N617" s="6"/>
       <c r="O617" s="6" t="s">
         <v>44</v>
@@ -52464,16 +52469,16 @@
         <v>66</v>
       </c>
       <c r="R617" s="6" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="S617" s="6" t="s">
-        <v>2269</v>
+        <v>2187</v>
       </c>
       <c r="T617" s="7" t="n">
-        <v>45908</v>
+        <v>42761</v>
       </c>
       <c r="U617" s="7" t="n">
-        <v>47717</v>
+        <v>46614</v>
       </c>
       <c r="V617" s="6"/>
       <c r="W617" s="6"/>
@@ -52488,30 +52493,34 @@
         <v>1104</v>
       </c>
       <c r="AF617" s="8" t="n">
-        <v>45908.6923148148</v>
-      </c>
-      <c r="AG617" s="6"/>
-      <c r="AH617" s="8"/>
+        <v>45816.6759837963</v>
+      </c>
+      <c r="AG617" s="6" t="s">
+        <v>1259</v>
+      </c>
+      <c r="AH617" s="8" t="n">
+        <v>45831.8282060185</v>
+      </c>
       <c r="AI617" s="6"/>
     </row>
     <row r="618" customHeight="1" ht="20">
       <c r="A618" s="5" t="n">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="B618" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C618" s="6" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="D618" s="6" t="s">
-        <v>2271</v>
+        <v>113</v>
       </c>
       <c r="E618" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F618" s="5" t="n">
-        <v>69135</v>
+        <v>72223</v>
       </c>
       <c r="G618" s="6" t="s">
         <v>2272</v>
@@ -52520,7 +52529,7 @@
         <v>68588</v>
       </c>
       <c r="I618" s="7" t="n">
-        <v>21906</v>
+        <v>23611</v>
       </c>
       <c r="J618" s="6" t="s">
         <v>40</v>
@@ -52551,10 +52560,10 @@
         <v>2277</v>
       </c>
       <c r="T618" s="7" t="n">
-        <v>44245</v>
+        <v>45908</v>
       </c>
       <c r="U618" s="7" t="n">
-        <v>48204</v>
+        <v>47717</v>
       </c>
       <c r="V618" s="6"/>
       <c r="W618" s="6"/>
@@ -52569,45 +52578,39 @@
         <v>1104</v>
       </c>
       <c r="AF618" s="8" t="n">
-        <v>45908</v>
-      </c>
-      <c r="AG618" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH618" s="8" t="n">
-        <v>45908</v>
-      </c>
-      <c r="AI618" s="6" t="s">
-        <v>2278</v>
-      </c>
+        <v>45908.6923148148</v>
+      </c>
+      <c r="AG618" s="6"/>
+      <c r="AH618" s="8"/>
+      <c r="AI618" s="6"/>
     </row>
     <row r="619" customHeight="1" ht="20">
       <c r="A619" s="5" t="n">
-        <v>3523</v>
+        <v>3504</v>
       </c>
       <c r="B619" s="6" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C619" s="6" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D619" s="6" t="s">
         <v>2279</v>
       </c>
-      <c r="D619" s="6" t="s">
-        <v>168</v>
-      </c>
       <c r="E619" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F619" s="5" t="n">
-        <v>68362</v>
+        <v>69135</v>
       </c>
       <c r="G619" s="6" t="s">
         <v>2280</v>
       </c>
       <c r="H619" s="5" t="n">
-        <v>73549</v>
+        <v>68588</v>
       </c>
       <c r="I619" s="7" t="n">
-        <v>25443</v>
+        <v>21906</v>
       </c>
       <c r="J619" s="6" t="s">
         <v>40</v>
@@ -52638,10 +52641,10 @@
         <v>2285</v>
       </c>
       <c r="T619" s="7" t="n">
-        <v>43818</v>
+        <v>44245</v>
       </c>
       <c r="U619" s="7" t="n">
-        <v>47723</v>
+        <v>48204</v>
       </c>
       <c r="V619" s="6"/>
       <c r="W619" s="6"/>
@@ -52656,51 +52659,57 @@
         <v>1104</v>
       </c>
       <c r="AF619" s="8" t="n">
-        <v>45911.2590277778</v>
-      </c>
-      <c r="AG619" s="6"/>
-      <c r="AH619" s="8"/>
-      <c r="AI619" s="6"/>
+        <v>45908</v>
+      </c>
+      <c r="AG619" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH619" s="8" t="n">
+        <v>45908</v>
+      </c>
+      <c r="AI619" s="6" t="s">
+        <v>2286</v>
+      </c>
     </row>
     <row r="620" customHeight="1" ht="20">
       <c r="A620" s="5" t="n">
-        <v>3526</v>
+        <v>3523</v>
       </c>
       <c r="B620" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C620" s="6" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="D620" s="6" t="s">
-        <v>440</v>
+        <v>168</v>
       </c>
       <c r="E620" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F620" s="5" t="n">
-        <v>69135</v>
+        <v>68362</v>
       </c>
       <c r="G620" s="6" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="H620" s="5" t="n">
-        <v>68588</v>
+        <v>73549</v>
       </c>
       <c r="I620" s="7" t="n">
-        <v>23445</v>
+        <v>25443</v>
       </c>
       <c r="J620" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K620" s="6" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="L620" s="6" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="M620" s="6" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="N620" s="6"/>
       <c r="O620" s="6" t="s">
@@ -52713,16 +52722,16 @@
         <v>66</v>
       </c>
       <c r="R620" s="6" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="S620" s="6" t="s">
-        <v>2277</v>
+        <v>2293</v>
       </c>
       <c r="T620" s="7" t="n">
-        <v>44517</v>
+        <v>43818</v>
       </c>
       <c r="U620" s="7" t="n">
-        <v>48282</v>
+        <v>47723</v>
       </c>
       <c r="V620" s="6"/>
       <c r="W620" s="6"/>
@@ -52737,7 +52746,7 @@
         <v>1104</v>
       </c>
       <c r="AF620" s="8" t="n">
-        <v>45911.422662037</v>
+        <v>45911.2590277778</v>
       </c>
       <c r="AG620" s="6"/>
       <c r="AH620" s="8"/>
@@ -52745,43 +52754,43 @@
     </row>
     <row r="621" customHeight="1" ht="20">
       <c r="A621" s="5" t="n">
-        <v>3589</v>
+        <v>3526</v>
       </c>
       <c r="B621" s="6" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C621" s="6" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="D621" s="6" t="s">
-        <v>2293</v>
+        <v>440</v>
       </c>
       <c r="E621" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F621" s="5" t="n">
-        <v>72881</v>
+        <v>69135</v>
       </c>
       <c r="G621" s="6" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="H621" s="5" t="n">
-        <v>73084</v>
+        <v>68588</v>
       </c>
       <c r="I621" s="7" t="n">
-        <v>20746</v>
+        <v>23445</v>
       </c>
       <c r="J621" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K621" s="6" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="L621" s="6" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="M621" s="6" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="N621" s="6"/>
       <c r="O621" s="6" t="s">
@@ -52791,19 +52800,19 @@
         <v>44</v>
       </c>
       <c r="Q621" s="6" t="s">
-        <v>469</v>
+        <v>66</v>
       </c>
       <c r="R621" s="6" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="S621" s="6" t="s">
-        <v>2299</v>
+        <v>2285</v>
       </c>
       <c r="T621" s="7" t="n">
-        <v>44655</v>
+        <v>44517</v>
       </c>
       <c r="U621" s="7" t="n">
-        <v>46313</v>
+        <v>48282</v>
       </c>
       <c r="V621" s="6"/>
       <c r="W621" s="6"/>
@@ -52818,7 +52827,7 @@
         <v>1104</v>
       </c>
       <c r="AF621" s="8" t="n">
-        <v>45935.472974537</v>
+        <v>45911.422662037</v>
       </c>
       <c r="AG621" s="6"/>
       <c r="AH621" s="8"/>
@@ -52826,7 +52835,7 @@
     </row>
     <row r="622" customHeight="1" ht="20">
       <c r="A622" s="5" t="n">
-        <v>3603</v>
+        <v>3589</v>
       </c>
       <c r="B622" s="6" t="s">
         <v>35</v>
@@ -52841,19 +52850,19 @@
         <v>38</v>
       </c>
       <c r="F622" s="5" t="n">
-        <v>75870</v>
+        <v>72881</v>
       </c>
       <c r="G622" s="6" t="s">
         <v>2302</v>
       </c>
       <c r="H622" s="5" t="n">
-        <v>75870</v>
+        <v>73084</v>
       </c>
       <c r="I622" s="7" t="n">
-        <v>25575</v>
+        <v>20746</v>
       </c>
       <c r="J622" s="6" t="s">
-        <v>678</v>
+        <v>40</v>
       </c>
       <c r="K622" s="6" t="s">
         <v>2303</v>
@@ -52861,7 +52870,9 @@
       <c r="L622" s="6" t="s">
         <v>2304</v>
       </c>
-      <c r="M622" s="6"/>
+      <c r="M622" s="6" t="s">
+        <v>2305</v>
+      </c>
       <c r="N622" s="6"/>
       <c r="O622" s="6" t="s">
         <v>44</v>
@@ -52870,19 +52881,19 @@
         <v>44</v>
       </c>
       <c r="Q622" s="6" t="s">
-        <v>66</v>
+        <v>469</v>
       </c>
       <c r="R622" s="6" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="S622" s="6" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="T622" s="7" t="n">
-        <v>45867</v>
+        <v>44655</v>
       </c>
       <c r="U622" s="7" t="n">
-        <v>49518</v>
+        <v>46313</v>
       </c>
       <c r="V622" s="6"/>
       <c r="W622" s="6"/>
@@ -52897,7 +52908,7 @@
         <v>1104</v>
       </c>
       <c r="AF622" s="8" t="n">
-        <v>45938.6088541667</v>
+        <v>45935.472974537</v>
       </c>
       <c r="AG622" s="6"/>
       <c r="AH622" s="8"/>
@@ -52905,40 +52916,40 @@
     </row>
     <row r="623" customHeight="1" ht="20">
       <c r="A623" s="5" t="n">
-        <v>3706</v>
+        <v>3603</v>
       </c>
       <c r="B623" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C623" s="6" t="s">
-        <v>2226</v>
+        <v>2308</v>
       </c>
       <c r="D623" s="6" t="s">
-        <v>492</v>
+        <v>2309</v>
       </c>
       <c r="E623" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F623" s="5" t="n">
-        <v>69952</v>
+        <v>75870</v>
       </c>
       <c r="G623" s="6" t="s">
-        <v>2227</v>
+        <v>2310</v>
       </c>
       <c r="H623" s="5" t="n">
-        <v>66179</v>
+        <v>75870</v>
       </c>
       <c r="I623" s="7" t="n">
-        <v>37754</v>
+        <v>25575</v>
       </c>
       <c r="J623" s="6" t="s">
-        <v>40</v>
+        <v>678</v>
       </c>
       <c r="K623" s="6" t="s">
-        <v>2307</v>
+        <v>2311</v>
       </c>
       <c r="L623" s="6" t="s">
-        <v>2308</v>
+        <v>2312</v>
       </c>
       <c r="M623" s="6"/>
       <c r="N623" s="6"/>
@@ -52952,16 +52963,16 @@
         <v>66</v>
       </c>
       <c r="R623" s="6" t="s">
-        <v>2309</v>
+        <v>2313</v>
       </c>
       <c r="S623" s="6" t="s">
-        <v>2232</v>
+        <v>2314</v>
       </c>
       <c r="T623" s="7" t="n">
-        <v>45813</v>
+        <v>45867</v>
       </c>
       <c r="U623" s="7" t="n">
-        <v>49442</v>
+        <v>49518</v>
       </c>
       <c r="V623" s="6"/>
       <c r="W623" s="6"/>
@@ -52976,7 +52987,7 @@
         <v>1104</v>
       </c>
       <c r="AF623" s="8" t="n">
-        <v>45982.3887615741</v>
+        <v>45938.6088541667</v>
       </c>
       <c r="AG623" s="6"/>
       <c r="AH623" s="8"/>
@@ -52984,40 +52995,40 @@
     </row>
     <row r="624" customHeight="1" ht="20">
       <c r="A624" s="5" t="n">
-        <v>3768</v>
+        <v>3706</v>
       </c>
       <c r="B624" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C624" s="6" t="s">
-        <v>2310</v>
+        <v>2234</v>
       </c>
       <c r="D624" s="6" t="s">
-        <v>2311</v>
+        <v>492</v>
       </c>
       <c r="E624" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F624" s="5" t="n">
-        <v>71734</v>
+        <v>69952</v>
       </c>
       <c r="G624" s="6" t="s">
-        <v>2312</v>
+        <v>2235</v>
       </c>
       <c r="H624" s="5" t="n">
-        <v>66434</v>
+        <v>66179</v>
       </c>
       <c r="I624" s="7" t="n">
-        <v>33161</v>
+        <v>37754</v>
       </c>
       <c r="J624" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K624" s="6" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="L624" s="6" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="M624" s="6"/>
       <c r="N624" s="6"/>
@@ -53031,16 +53042,16 @@
         <v>66</v>
       </c>
       <c r="R624" s="6" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="S624" s="6" t="s">
-        <v>2316</v>
+        <v>2240</v>
       </c>
       <c r="T624" s="7" t="n">
-        <v>45017</v>
+        <v>45813</v>
       </c>
       <c r="U624" s="7" t="n">
-        <v>48505</v>
+        <v>49442</v>
       </c>
       <c r="V624" s="6"/>
       <c r="W624" s="6"/>
@@ -53055,56 +53066,50 @@
         <v>1104</v>
       </c>
       <c r="AF624" s="8" t="n">
-        <v>45994.5996875</v>
-      </c>
-      <c r="AG624" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH624" s="8" t="n">
-        <v>45994.6957060185</v>
-      </c>
+        <v>45982.3887615741</v>
+      </c>
+      <c r="AG624" s="6"/>
+      <c r="AH624" s="8"/>
       <c r="AI624" s="6"/>
     </row>
     <row r="625" customHeight="1" ht="20">
       <c r="A625" s="5" t="n">
-        <v>3784</v>
+        <v>3768</v>
       </c>
       <c r="B625" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C625" s="6" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="D625" s="6" t="s">
-        <v>71</v>
+        <v>2319</v>
       </c>
       <c r="E625" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F625" s="5" t="n">
-        <v>69903</v>
+        <v>71734</v>
       </c>
       <c r="G625" s="6" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="H625" s="5" t="n">
-        <v>69903</v>
+        <v>66434</v>
       </c>
       <c r="I625" s="7" t="n">
-        <v>30461</v>
+        <v>33161</v>
       </c>
       <c r="J625" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K625" s="6" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="L625" s="6" t="s">
-        <v>2320</v>
-      </c>
-      <c r="M625" s="6" t="s">
-        <v>2321</v>
-      </c>
+        <v>2322</v>
+      </c>
+      <c r="M625" s="6"/>
       <c r="N625" s="6"/>
       <c r="O625" s="6" t="s">
         <v>44</v>
@@ -53116,16 +53121,16 @@
         <v>66</v>
       </c>
       <c r="R625" s="6" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="S625" s="6" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="T625" s="7" t="n">
-        <v>43532</v>
+        <v>45017</v>
       </c>
       <c r="U625" s="7" t="n">
-        <v>47263</v>
+        <v>48505</v>
       </c>
       <c r="V625" s="6"/>
       <c r="W625" s="6"/>
@@ -53140,51 +53145,55 @@
         <v>1104</v>
       </c>
       <c r="AF625" s="8" t="n">
-        <v>45999.4221296296</v>
-      </c>
-      <c r="AG625" s="6"/>
-      <c r="AH625" s="8"/>
+        <v>45994.5996875</v>
+      </c>
+      <c r="AG625" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH625" s="8" t="n">
+        <v>45994.6957060185</v>
+      </c>
       <c r="AI625" s="6"/>
     </row>
     <row r="626" customHeight="1" ht="20">
       <c r="A626" s="5" t="n">
-        <v>3813</v>
+        <v>3784</v>
       </c>
       <c r="B626" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C626" s="6" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="D626" s="6" t="s">
-        <v>241</v>
+        <v>71</v>
       </c>
       <c r="E626" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F626" s="5" t="n">
-        <v>71300</v>
+        <v>69903</v>
       </c>
       <c r="G626" s="6" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="H626" s="5" t="n">
-        <v>73084</v>
+        <v>69903</v>
       </c>
       <c r="I626" s="7" t="n">
-        <v>35285</v>
+        <v>30461</v>
       </c>
       <c r="J626" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K626" s="6" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="L626" s="6" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="M626" s="6" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="N626" s="6"/>
       <c r="O626" s="6" t="s">
@@ -53194,19 +53203,19 @@
         <v>44</v>
       </c>
       <c r="Q626" s="6" t="s">
-        <v>469</v>
+        <v>66</v>
       </c>
       <c r="R626" s="6" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="S626" s="6" t="s">
-        <v>2260</v>
+        <v>2331</v>
       </c>
       <c r="T626" s="7" t="n">
-        <v>45497</v>
+        <v>43532</v>
       </c>
       <c r="U626" s="7" t="n">
-        <v>49164</v>
+        <v>47263</v>
       </c>
       <c r="V626" s="6"/>
       <c r="W626" s="6"/>
@@ -53221,7 +53230,7 @@
         <v>1104</v>
       </c>
       <c r="AF626" s="8" t="n">
-        <v>46002.852962963</v>
+        <v>45999.4221296296</v>
       </c>
       <c r="AG626" s="6"/>
       <c r="AH626" s="8"/>
@@ -53229,16 +53238,16 @@
     </row>
     <row r="627" customHeight="1" ht="20">
       <c r="A627" s="5" t="n">
-        <v>3817</v>
+        <v>3813</v>
       </c>
       <c r="B627" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C627" s="6" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="D627" s="6" t="s">
-        <v>1041</v>
+        <v>241</v>
       </c>
       <c r="E627" s="6" t="s">
         <v>38</v>
@@ -53247,25 +53256,25 @@
         <v>71300</v>
       </c>
       <c r="G627" s="6" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="H627" s="5" t="n">
-        <v>67182</v>
+        <v>73084</v>
       </c>
       <c r="I627" s="7" t="n">
-        <v>34869</v>
+        <v>35285</v>
       </c>
       <c r="J627" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K627" s="6" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="L627" s="6" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="M627" s="6" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="N627" s="6"/>
       <c r="O627" s="6" t="s">
@@ -53275,19 +53284,19 @@
         <v>44</v>
       </c>
       <c r="Q627" s="6" t="s">
-        <v>66</v>
+        <v>469</v>
       </c>
       <c r="R627" s="6" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="S627" s="6" t="s">
-        <v>2336</v>
+        <v>2268</v>
       </c>
       <c r="T627" s="7" t="n">
-        <v>45567</v>
+        <v>45497</v>
       </c>
       <c r="U627" s="7" t="n">
-        <v>49114</v>
+        <v>49164</v>
       </c>
       <c r="V627" s="6"/>
       <c r="W627" s="6"/>
@@ -53302,7 +53311,7 @@
         <v>1104</v>
       </c>
       <c r="AF627" s="8" t="n">
-        <v>46002.8803356481</v>
+        <v>46002.852962963</v>
       </c>
       <c r="AG627" s="6"/>
       <c r="AH627" s="8"/>
@@ -53310,43 +53319,43 @@
     </row>
     <row r="628" customHeight="1" ht="20">
       <c r="A628" s="5" t="n">
-        <v>3864</v>
+        <v>3817</v>
       </c>
       <c r="B628" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C628" s="6" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="D628" s="6" t="s">
-        <v>241</v>
+        <v>1041</v>
       </c>
       <c r="E628" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F628" s="5" t="n">
-        <v>71700</v>
+        <v>71300</v>
       </c>
       <c r="G628" s="6" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="H628" s="5" t="n">
-        <v>71700</v>
+        <v>67182</v>
       </c>
       <c r="I628" s="7" t="n">
-        <v>36959</v>
+        <v>34869</v>
       </c>
       <c r="J628" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K628" s="6" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="L628" s="6" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="M628" s="6" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="N628" s="6"/>
       <c r="O628" s="6" t="s">
@@ -53356,19 +53365,19 @@
         <v>44</v>
       </c>
       <c r="Q628" s="6" t="s">
-        <v>469</v>
+        <v>66</v>
       </c>
       <c r="R628" s="6" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="S628" s="6" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="T628" s="7" t="n">
-        <v>45808</v>
+        <v>45567</v>
       </c>
       <c r="U628" s="7" t="n">
-        <v>46451</v>
+        <v>49114</v>
       </c>
       <c r="V628" s="6"/>
       <c r="W628" s="6"/>
@@ -53383,7 +53392,7 @@
         <v>1104</v>
       </c>
       <c r="AF628" s="8" t="n">
-        <v>46014.5767939815</v>
+        <v>46002.8803356481</v>
       </c>
       <c r="AG628" s="6"/>
       <c r="AH628" s="8"/>
@@ -53391,43 +53400,43 @@
     </row>
     <row r="629" customHeight="1" ht="20">
       <c r="A629" s="5" t="n">
-        <v>3866</v>
+        <v>3864</v>
       </c>
       <c r="B629" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C629" s="6" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="D629" s="6" t="s">
-        <v>348</v>
+        <v>241</v>
       </c>
       <c r="E629" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F629" s="5" t="n">
-        <v>71821</v>
+        <v>71700</v>
       </c>
       <c r="G629" s="6" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="H629" s="5" t="n">
-        <v>70685</v>
+        <v>71700</v>
       </c>
       <c r="I629" s="7" t="n">
-        <v>22552</v>
+        <v>36959</v>
       </c>
       <c r="J629" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K629" s="6" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="L629" s="6" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="M629" s="6" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="N629" s="6"/>
       <c r="O629" s="6" t="s">
@@ -53437,19 +53446,19 @@
         <v>44</v>
       </c>
       <c r="Q629" s="6" t="s">
-        <v>66</v>
+        <v>469</v>
       </c>
       <c r="R629" s="6" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="S629" s="6" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="T629" s="7" t="n">
-        <v>43483</v>
+        <v>45808</v>
       </c>
       <c r="U629" s="7" t="n">
-        <v>47389</v>
+        <v>46451</v>
       </c>
       <c r="V629" s="6"/>
       <c r="W629" s="6"/>
@@ -53464,7 +53473,7 @@
         <v>1104</v>
       </c>
       <c r="AF629" s="8" t="n">
-        <v>46014.7612384259</v>
+        <v>46014.5767939815</v>
       </c>
       <c r="AG629" s="6"/>
       <c r="AH629" s="8"/>
@@ -53472,43 +53481,43 @@
     </row>
     <row r="630" customHeight="1" ht="20">
       <c r="A630" s="5" t="n">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="B630" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C630" s="6" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="D630" s="6" t="s">
-        <v>277</v>
+        <v>348</v>
       </c>
       <c r="E630" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F630" s="5" t="n">
-        <v>68226</v>
+        <v>71821</v>
       </c>
       <c r="G630" s="6" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="H630" s="5" t="n">
-        <v>73033</v>
+        <v>70685</v>
       </c>
       <c r="I630" s="7" t="n">
-        <v>29108</v>
+        <v>22552</v>
       </c>
       <c r="J630" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K630" s="6" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="L630" s="6" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="M630" s="6" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="N630" s="6"/>
       <c r="O630" s="6" t="s">
@@ -53518,19 +53527,19 @@
         <v>44</v>
       </c>
       <c r="Q630" s="6" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="R630" s="6" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="S630" s="6" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="T630" s="7" t="n">
-        <v>43676</v>
+        <v>43483</v>
       </c>
       <c r="U630" s="7" t="n">
-        <v>47328</v>
+        <v>47389</v>
       </c>
       <c r="V630" s="6"/>
       <c r="W630" s="6"/>
@@ -53545,7 +53554,7 @@
         <v>1104</v>
       </c>
       <c r="AF630" s="8" t="n">
-        <v>46014.7663773148</v>
+        <v>46014.7612384259</v>
       </c>
       <c r="AG630" s="6"/>
       <c r="AH630" s="8"/>
@@ -53553,31 +53562,31 @@
     </row>
     <row r="631" customHeight="1" ht="20">
       <c r="A631" s="5" t="n">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="B631" s="6" t="s">
         <v>124</v>
       </c>
       <c r="C631" s="6" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="D631" s="6" t="s">
-        <v>2359</v>
+        <v>277</v>
       </c>
       <c r="E631" s="6" t="s">
         <v>127</v>
       </c>
       <c r="F631" s="5" t="n">
-        <v>69373</v>
+        <v>68226</v>
       </c>
       <c r="G631" s="6" t="s">
         <v>2360</v>
       </c>
       <c r="H631" s="5" t="n">
-        <v>67855</v>
+        <v>73033</v>
       </c>
       <c r="I631" s="7" t="n">
-        <v>28475</v>
+        <v>29108</v>
       </c>
       <c r="J631" s="6" t="s">
         <v>40</v>
@@ -53608,10 +53617,10 @@
         <v>2365</v>
       </c>
       <c r="T631" s="7" t="n">
-        <v>45471</v>
+        <v>43676</v>
       </c>
       <c r="U631" s="7" t="n">
-        <v>49122</v>
+        <v>47328</v>
       </c>
       <c r="V631" s="6"/>
       <c r="W631" s="6"/>
@@ -53626,55 +53635,51 @@
         <v>1104</v>
       </c>
       <c r="AF631" s="8" t="n">
-        <v>46014.8041435185</v>
-      </c>
-      <c r="AG631" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH631" s="8" t="n">
-        <v>46014.8068171296</v>
-      </c>
+        <v>46014.7663773148</v>
+      </c>
+      <c r="AG631" s="6"/>
+      <c r="AH631" s="8"/>
       <c r="AI631" s="6"/>
     </row>
     <row r="632" customHeight="1" ht="20">
       <c r="A632" s="5" t="n">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="B632" s="6" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C632" s="6" t="s">
         <v>2366</v>
       </c>
       <c r="D632" s="6" t="s">
-        <v>1590</v>
+        <v>2367</v>
       </c>
       <c r="E632" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F632" s="5" t="n">
         <v>69373</v>
       </c>
       <c r="G632" s="6" t="s">
-        <v>2360</v>
+        <v>2368</v>
       </c>
       <c r="H632" s="5" t="n">
-        <v>69288</v>
+        <v>67855</v>
       </c>
       <c r="I632" s="7" t="n">
-        <v>27438</v>
+        <v>28475</v>
       </c>
       <c r="J632" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K632" s="6" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="L632" s="6" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="M632" s="6" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="N632" s="6"/>
       <c r="O632" s="6" t="s">
@@ -53687,16 +53692,16 @@
         <v>45</v>
       </c>
       <c r="R632" s="6" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="S632" s="6" t="s">
-        <v>2365</v>
+        <v>2373</v>
       </c>
       <c r="T632" s="7" t="n">
-        <v>44901</v>
+        <v>45471</v>
       </c>
       <c r="U632" s="7" t="n">
-        <v>48553</v>
+        <v>49122</v>
       </c>
       <c r="V632" s="6"/>
       <c r="W632" s="6"/>
@@ -53711,51 +53716,55 @@
         <v>1104</v>
       </c>
       <c r="AF632" s="8" t="n">
-        <v>46014.8127546296</v>
-      </c>
-      <c r="AG632" s="6"/>
-      <c r="AH632" s="8"/>
+        <v>46014.8041435185</v>
+      </c>
+      <c r="AG632" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH632" s="8" t="n">
+        <v>46014.8068171296</v>
+      </c>
       <c r="AI632" s="6"/>
     </row>
     <row r="633" customHeight="1" ht="20">
       <c r="A633" s="5" t="n">
-        <v>3888</v>
+        <v>3869</v>
       </c>
       <c r="B633" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C633" s="6" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="D633" s="6" t="s">
-        <v>101</v>
+        <v>1590</v>
       </c>
       <c r="E633" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F633" s="5" t="n">
-        <v>72957</v>
+        <v>69373</v>
       </c>
       <c r="G633" s="6" t="s">
-        <v>2372</v>
+        <v>2368</v>
       </c>
       <c r="H633" s="5" t="n">
-        <v>76150</v>
+        <v>69288</v>
       </c>
       <c r="I633" s="7" t="n">
-        <v>26041</v>
+        <v>27438</v>
       </c>
       <c r="J633" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K633" s="6" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="L633" s="6" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="M633" s="6" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="N633" s="6"/>
       <c r="O633" s="6" t="s">
@@ -53765,19 +53774,19 @@
         <v>44</v>
       </c>
       <c r="Q633" s="6" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="R633" s="6" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="S633" s="6" t="s">
-        <v>2377</v>
+        <v>2373</v>
       </c>
       <c r="T633" s="7" t="n">
-        <v>43362</v>
+        <v>44901</v>
       </c>
       <c r="U633" s="7" t="n">
-        <v>47226</v>
+        <v>48553</v>
       </c>
       <c r="V633" s="6"/>
       <c r="W633" s="6"/>
@@ -53792,55 +53801,51 @@
         <v>1104</v>
       </c>
       <c r="AF633" s="8" t="n">
-        <v>46030</v>
-      </c>
-      <c r="AG633" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH633" s="8" t="n">
-        <v>46031</v>
-      </c>
+        <v>46014.8127546296</v>
+      </c>
+      <c r="AG633" s="6"/>
+      <c r="AH633" s="8"/>
       <c r="AI633" s="6"/>
     </row>
     <row r="634" customHeight="1" ht="20">
       <c r="A634" s="5" t="n">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="B634" s="6" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C634" s="6" t="s">
-        <v>209</v>
+        <v>2379</v>
       </c>
       <c r="D634" s="6" t="s">
-        <v>668</v>
+        <v>101</v>
       </c>
       <c r="E634" s="6" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="F634" s="5" t="n">
-        <v>66434</v>
+        <v>72957</v>
       </c>
       <c r="G634" s="6" t="s">
-        <v>1107</v>
+        <v>2380</v>
       </c>
       <c r="H634" s="5" t="n">
-        <v>66434</v>
+        <v>76150</v>
       </c>
       <c r="I634" s="7" t="n">
-        <v>23522</v>
+        <v>26041</v>
       </c>
       <c r="J634" s="6" t="s">
         <v>40</v>
       </c>
       <c r="K634" s="6" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="L634" s="6" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
       <c r="M634" s="6" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="N634" s="6"/>
       <c r="O634" s="6" t="s">
@@ -53853,16 +53858,16 @@
         <v>66</v>
       </c>
       <c r="R634" s="6" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="S634" s="6" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="T634" s="7" t="n">
-        <v>45086</v>
+        <v>43362</v>
       </c>
       <c r="U634" s="7" t="n">
-        <v>48724</v>
+        <v>47226</v>
       </c>
       <c r="V634" s="6"/>
       <c r="W634" s="6"/>
@@ -53877,13 +53882,15 @@
         <v>1104</v>
       </c>
       <c r="AF634" s="8" t="n">
-        <v>46031.4429398148</v>
-      </c>
-      <c r="AG634" s="6"/>
-      <c r="AH634" s="8"/>
-      <c r="AI634" s="6" t="s">
-        <v>2383</v>
-      </c>
+        <v>46030</v>
+      </c>
+      <c r="AG634" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH634" s="8" t="n">
+        <v>46031</v>
+      </c>
+      <c r="AI634" s="6"/>
     </row>
     <row r="635" customHeight="1" ht="20">
       <c r="A635" s="5" t="n">
@@ -53893,7 +53900,7 @@
         <v>35</v>
       </c>
       <c r="C635" s="6" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="D635" s="6" t="s">
         <v>113</v>
@@ -53905,7 +53912,7 @@
         <v>73595</v>
       </c>
       <c r="G635" s="6" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="H635" s="5" t="n">
         <v>68560</v>
@@ -53917,13 +53924,13 @@
         <v>40</v>
       </c>
       <c r="K635" s="6" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="L635" s="6" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="M635" s="6" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
       <c r="N635" s="6"/>
       <c r="O635" s="6" t="s">
@@ -53936,10 +53943,10 @@
         <v>66</v>
       </c>
       <c r="R635" s="6" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="S635" s="6" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="T635" s="7" t="n">
         <v>44221</v>
@@ -53974,10 +53981,10 @@
         <v>124</v>
       </c>
       <c r="C636" s="6" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="D636" s="6" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="E636" s="6" t="s">
         <v>127</v>
@@ -53986,7 +53993,7 @@
         <v>73595</v>
       </c>
       <c r="G636" s="6" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="H636" s="5" t="n">
         <v>68560</v>
@@ -53998,13 +54005,13 @@
         <v>40</v>
       </c>
       <c r="K636" s="6" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="L636" s="6" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="M636" s="6" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="N636" s="6"/>
       <c r="O636" s="6" t="s">
@@ -54017,10 +54024,10 @@
         <v>66</v>
       </c>
       <c r="R636" s="6" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="S636" s="6" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="T636" s="7" t="n">
         <v>44656</v>
@@ -54055,7 +54062,7 @@
         <v>35</v>
       </c>
       <c r="C637" s="6" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="D637" s="6" t="s">
         <v>602</v>
@@ -54067,7 +54074,7 @@
         <v>71700</v>
       </c>
       <c r="G637" s="6" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="H637" s="5" t="n">
         <v>71700</v>
@@ -54079,13 +54086,13 @@
         <v>40</v>
       </c>
       <c r="K637" s="6" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="L637" s="6" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="M637" s="6" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="N637" s="6"/>
       <c r="O637" s="6" t="s">
@@ -54098,10 +54105,10 @@
         <v>469</v>
       </c>
       <c r="R637" s="6" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="S637" s="6" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="T637" s="7" t="n">
         <v>45033</v>
@@ -54136,7 +54143,7 @@
         <v>124</v>
       </c>
       <c r="C638" s="6" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D638" s="6" t="s">
         <v>1261</v>
@@ -54148,7 +54155,7 @@
         <v>71700</v>
       </c>
       <c r="G638" s="6" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="H638" s="5" t="n">
         <v>71700</v>
@@ -54160,13 +54167,13 @@
         <v>40</v>
       </c>
       <c r="K638" s="6" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="L638" s="6" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="M638" s="6" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="N638" s="6"/>
       <c r="O638" s="6" t="s">
@@ -54179,10 +54186,10 @@
         <v>469</v>
       </c>
       <c r="R638" s="6" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="S638" s="6" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="T638" s="7" t="n">
         <v>45539</v>
@@ -54217,10 +54224,10 @@
         <v>35</v>
       </c>
       <c r="C639" s="6" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="D639" s="6" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="E639" s="6" t="s">
         <v>38</v>
@@ -54229,7 +54236,7 @@
         <v>71700</v>
       </c>
       <c r="G639" s="6" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="H639" s="5" t="n">
         <v>71700</v>
@@ -54241,13 +54248,13 @@
         <v>40</v>
       </c>
       <c r="K639" s="6" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="L639" s="6" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="M639" s="6" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="N639" s="6"/>
       <c r="O639" s="6" t="s">
@@ -54260,10 +54267,10 @@
         <v>66</v>
       </c>
       <c r="R639" s="6" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="S639" s="6" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="T639" s="7" t="n">
         <v>43704</v>
@@ -54298,7 +54305,7 @@
         <v>35</v>
       </c>
       <c r="C640" s="6" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="D640" s="6" t="s">
         <v>703</v>
@@ -54310,7 +54317,7 @@
         <v>68588</v>
       </c>
       <c r="G640" s="6" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="H640" s="5" t="n">
         <v>68588</v>
@@ -54322,13 +54329,13 @@
         <v>40</v>
       </c>
       <c r="K640" s="6" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="L640" s="6" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="M640" s="6" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="N640" s="6"/>
       <c r="O640" s="6" t="s">
@@ -54341,10 +54348,10 @@
         <v>66</v>
       </c>
       <c r="R640" s="6" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="S640" s="6" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="T640" s="7" t="n">
         <v>44673</v>
@@ -54374,7 +54381,7 @@
         <v>45946.7970949074</v>
       </c>
       <c r="AI640" s="6" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="641" customHeight="1" ht="20">
@@ -54385,10 +54392,10 @@
         <v>124</v>
       </c>
       <c r="C641" s="6" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="D641" s="6" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="E641" s="6" t="s">
         <v>127</v>
@@ -54397,7 +54404,7 @@
         <v>68588</v>
       </c>
       <c r="G641" s="6" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="H641" s="5" t="n">
         <v>71197</v>
@@ -54409,13 +54416,13 @@
         <v>40</v>
       </c>
       <c r="K641" s="6" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="L641" s="6" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="M641" s="6" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="N641" s="6"/>
       <c r="O641" s="6" t="s">
@@ -54428,10 +54435,10 @@
         <v>66</v>
       </c>
       <c r="R641" s="6" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="S641" s="6" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="T641" s="7" t="n">
         <v>45503</v>
@@ -54469,7 +54476,7 @@
         <v>1252</v>
       </c>
       <c r="D642" s="6" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="E642" s="6" t="s">
         <v>38</v>
@@ -54478,7 +54485,7 @@
         <v>73868</v>
       </c>
       <c r="G642" s="6" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="H642" s="5" t="n">
         <v>72021</v>
@@ -54490,13 +54497,13 @@
         <v>40</v>
       </c>
       <c r="K642" s="6" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="L642" s="6" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="M642" s="6" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="N642" s="6"/>
       <c r="O642" s="6" t="s">
@@ -54509,10 +54516,10 @@
         <v>66</v>
       </c>
       <c r="R642" s="6" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="S642" s="6" t="s">
-        <v>2350</v>
+        <v>2358</v>
       </c>
       <c r="T642" s="7" t="n">
         <v>45887</v>
@@ -54547,10 +54554,10 @@
         <v>35</v>
       </c>
       <c r="C643" s="6" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="D643" s="6" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="E643" s="6" t="s">
         <v>38</v>
@@ -54559,7 +54566,7 @@
         <v>65966</v>
       </c>
       <c r="G643" s="6" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="H643" s="5" t="n">
         <v>72021</v>
@@ -54571,13 +54578,13 @@
         <v>40</v>
       </c>
       <c r="K643" s="6" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="L643" s="6" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="M643" s="6" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="N643" s="6"/>
       <c r="O643" s="6" t="s">
@@ -54590,10 +54597,10 @@
         <v>66</v>
       </c>
       <c r="R643" s="6" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="S643" s="6" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="T643" s="7" t="n">
         <v>44301</v>
@@ -54632,7 +54639,7 @@
         <v>35</v>
       </c>
       <c r="C644" s="6" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="D644" s="6" t="s">
         <v>89</v>
@@ -54644,7 +54651,7 @@
         <v>66459</v>
       </c>
       <c r="G644" s="6" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="H644" s="5" t="n">
         <v>69863</v>
@@ -54656,13 +54663,13 @@
         <v>40</v>
       </c>
       <c r="K644" s="6" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="L644" s="6" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="M644" s="6" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="N644" s="6"/>
       <c r="O644" s="6" t="s">
@@ -54675,10 +54682,10 @@
         <v>66</v>
       </c>
       <c r="R644" s="6" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="S644" s="6" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="T644" s="7" t="n">
         <v>43434</v>
@@ -54713,7 +54720,7 @@
         <v>35</v>
       </c>
       <c r="C645" s="6" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="D645" s="6" t="s">
         <v>1571</v>
@@ -54725,7 +54732,7 @@
         <v>67348</v>
       </c>
       <c r="G645" s="6" t="s">
-        <v>2220</v>
+        <v>2228</v>
       </c>
       <c r="H645" s="5" t="n">
         <v>72753</v>
@@ -54737,13 +54744,13 @@
         <v>40</v>
       </c>
       <c r="K645" s="6" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="L645" s="6" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="M645" s="6" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="N645" s="6"/>
       <c r="O645" s="6" t="s">
@@ -54756,10 +54763,10 @@
         <v>66</v>
       </c>
       <c r="R645" s="6" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="S645" s="6" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="T645" s="7" t="n">
         <v>43097</v>
@@ -54794,7 +54801,7 @@
         <v>35</v>
       </c>
       <c r="C646" s="6" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="D646" s="6" t="s">
         <v>524</v>
@@ -54806,7 +54813,7 @@
         <v>71575</v>
       </c>
       <c r="G646" s="6" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="H646" s="5" t="n">
         <v>71700</v>
@@ -54818,13 +54825,13 @@
         <v>40</v>
       </c>
       <c r="K646" s="6" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="L646" s="6" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="M646" s="6" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="N646" s="6"/>
       <c r="O646" s="6" t="s">
@@ -54837,10 +54844,10 @@
         <v>66</v>
       </c>
       <c r="R646" s="6" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="S646" s="6" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="T646" s="7" t="n">
         <v>45202</v>
@@ -54875,10 +54882,10 @@
         <v>35</v>
       </c>
       <c r="C647" s="6" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="D647" s="6" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="E647" s="6" t="s">
         <v>38</v>
@@ -54887,7 +54894,7 @@
         <v>71329</v>
       </c>
       <c r="G647" s="6" t="s">
-        <v>2235</v>
+        <v>2243</v>
       </c>
       <c r="H647" s="5" t="n">
         <v>70367</v>
@@ -54899,13 +54906,13 @@
         <v>40</v>
       </c>
       <c r="K647" s="6" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="L647" s="6" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="M647" s="6" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="N647" s="6"/>
       <c r="O647" s="6" t="s">
@@ -54918,10 +54925,10 @@
         <v>66</v>
       </c>
       <c r="R647" s="6" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="S647" s="6" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="T647" s="7" t="n">
         <v>44097</v>
@@ -54947,7 +54954,7 @@
       <c r="AG647" s="6"/>
       <c r="AH647" s="8"/>
       <c r="AI647" s="6" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="648" customHeight="1" ht="20">
@@ -54958,7 +54965,7 @@
         <v>35</v>
       </c>
       <c r="C648" s="6" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="D648" s="6" t="s">
         <v>95</v>
@@ -54970,7 +54977,7 @@
         <v>68662</v>
       </c>
       <c r="G648" s="6" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="H648" s="5" t="n">
         <v>68662</v>
@@ -54982,13 +54989,13 @@
         <v>40</v>
       </c>
       <c r="K648" s="6" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="L648" s="6" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="M648" s="6" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="N648" s="6"/>
       <c r="O648" s="6" t="s">
@@ -55001,10 +55008,10 @@
         <v>66</v>
       </c>
       <c r="R648" s="6" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="S648" s="6" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="T648" s="7" t="n">
         <v>45265</v>
@@ -55043,7 +55050,7 @@
         <v>124</v>
       </c>
       <c r="C649" s="6" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="D649" s="6" t="s">
         <v>665</v>
@@ -55055,7 +55062,7 @@
         <v>68662</v>
       </c>
       <c r="G649" s="6" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="H649" s="5" t="n">
         <v>69198</v>
@@ -55067,13 +55074,13 @@
         <v>40</v>
       </c>
       <c r="K649" s="6" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="L649" s="6" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="M649" s="6" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="N649" s="6"/>
       <c r="O649" s="6" t="s">
@@ -55086,10 +55093,10 @@
         <v>66</v>
       </c>
       <c r="R649" s="6" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="S649" s="6" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="T649" s="7" t="n">
         <v>43827</v>
@@ -55119,7 +55126,7 @@
         <v>45986.6269791667</v>
       </c>
       <c r="AI649" s="6" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="650" customHeight="1" ht="20">
@@ -55130,10 +55137,10 @@
         <v>124</v>
       </c>
       <c r="C650" s="6" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="D650" s="6" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="E650" s="6" t="s">
         <v>127</v>
@@ -55142,7 +55149,7 @@
         <v>66179</v>
       </c>
       <c r="G650" s="6" t="s">
-        <v>2241</v>
+        <v>2249</v>
       </c>
       <c r="H650" s="5" t="n">
         <v>66179</v>
@@ -55154,13 +55161,13 @@
         <v>40</v>
       </c>
       <c r="K650" s="6" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="L650" s="6" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="M650" s="6" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="N650" s="6"/>
       <c r="O650" s="6" t="s">
@@ -55173,10 +55180,10 @@
         <v>66</v>
       </c>
       <c r="R650" s="6" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="S650" s="6" t="s">
-        <v>2246</v>
+        <v>2254</v>
       </c>
       <c r="T650" s="7" t="n">
         <v>42562</v>
@@ -55211,7 +55218,7 @@
         <v>124</v>
       </c>
       <c r="C651" s="6" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="D651" s="6" t="s">
         <v>1616</v>
@@ -55223,7 +55230,7 @@
         <v>72518</v>
       </c>
       <c r="G651" s="6" t="s">
-        <v>2248</v>
+        <v>2256</v>
       </c>
       <c r="H651" s="5" t="n">
         <v>72518</v>
@@ -55235,13 +55242,13 @@
         <v>40</v>
       </c>
       <c r="K651" s="6" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="L651" s="6" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="M651" s="6" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="N651" s="6"/>
       <c r="O651" s="6" t="s">
@@ -55254,10 +55261,10 @@
         <v>66</v>
       </c>
       <c r="R651" s="6" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="S651" s="6" t="s">
-        <v>2253</v>
+        <v>2261</v>
       </c>
       <c r="T651" s="7" t="n">
         <v>44140</v>
@@ -55296,7 +55303,7 @@
         <v>35</v>
       </c>
       <c r="C652" s="6" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="D652" s="6" t="s">
         <v>71</v>
@@ -55308,7 +55315,7 @@
         <v>66434</v>
       </c>
       <c r="G652" s="6" t="s">
-        <v>2312</v>
+        <v>2320</v>
       </c>
       <c r="H652" s="5" t="n">
         <v>71189</v>
@@ -55320,10 +55327,10 @@
         <v>40</v>
       </c>
       <c r="K652" s="6" t="s">
-        <v>2313</v>
+        <v>2321</v>
       </c>
       <c r="L652" s="6" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="M652" s="6"/>
       <c r="N652" s="6"/>
@@ -55337,10 +55344,10 @@
         <v>469</v>
       </c>
       <c r="R652" s="6" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="S652" s="6" t="s">
-        <v>2316</v>
+        <v>2324</v>
       </c>
       <c r="T652" s="7" t="n">
         <v>44090</v>
@@ -55375,10 +55382,10 @@
         <v>35</v>
       </c>
       <c r="C653" s="6" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="D653" s="6" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="E653" s="6" t="s">
         <v>38</v>
@@ -55387,7 +55394,7 @@
         <v>66434</v>
       </c>
       <c r="G653" s="6" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="H653" s="5" t="n">
         <v>76131</v>
@@ -55399,13 +55406,13 @@
         <v>40</v>
       </c>
       <c r="K653" s="6" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="L653" s="6" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="M653" s="6" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="N653" s="6"/>
       <c r="O653" s="6" t="s">
@@ -55418,10 +55425,10 @@
         <v>66</v>
       </c>
       <c r="R653" s="6" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="S653" s="6" t="s">
-        <v>2382</v>
+        <v>2511</v>
       </c>
       <c r="T653" s="7" t="n">
         <v>45341</v>
@@ -55472,7 +55479,7 @@
         <v>69863</v>
       </c>
       <c r="G654" s="6" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="H654" s="5" t="n">
         <v>69863</v>
@@ -55484,13 +55491,13 @@
         <v>40</v>
       </c>
       <c r="K654" s="6" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="L654" s="6" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="M654" s="6" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
       <c r="N654" s="6"/>
       <c r="O654" s="6" t="s">
@@ -55503,7 +55510,7 @@
         <v>66</v>
       </c>
       <c r="R654" s="6" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="S654" s="6" t="s">
         <v>1975</v>
@@ -55548,7 +55555,7 @@
         <v>1052</v>
       </c>
       <c r="D655" s="6" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
       <c r="E655" s="6" t="s">
         <v>38</v>
@@ -55557,7 +55564,7 @@
         <v>69135</v>
       </c>
       <c r="G655" s="6" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
       <c r="H655" s="5" t="n">
         <v>68588</v>
@@ -55569,10 +55576,10 @@
         <v>40</v>
       </c>
       <c r="K655" s="6" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="L655" s="6" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
       <c r="M655" s="6"/>
       <c r="N655" s="6"/>
@@ -55586,10 +55593,10 @@
         <v>469</v>
       </c>
       <c r="R655" s="6" t="s">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="S655" s="6" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="T655" s="7" t="n">
         <v>31978</v>
@@ -55615,7 +55622,7 @@
       <c r="AG655" s="6"/>
       <c r="AH655" s="8"/>
       <c r="AI655" s="6" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="656" customHeight="1" ht="20">
@@ -55626,10 +55633,10 @@
         <v>35</v>
       </c>
       <c r="C656" s="6" t="s">
-        <v>2521</v>
+        <v>2524</v>
       </c>
       <c r="D656" s="6" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="E656" s="6" t="s">
         <v>38</v>
@@ -55638,7 +55645,7 @@
         <v>71300</v>
       </c>
       <c r="G656" s="6" t="s">
-        <v>2331</v>
+        <v>2339</v>
       </c>
       <c r="H656" s="5" t="n">
         <v>67182</v>
@@ -55650,13 +55657,13 @@
         <v>40</v>
       </c>
       <c r="K656" s="6" t="s">
-        <v>2332</v>
+        <v>2340</v>
       </c>
       <c r="L656" s="6" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="M656" s="6" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
       <c r="N656" s="6"/>
       <c r="O656" s="6" t="s">
@@ -55669,10 +55676,10 @@
         <v>66</v>
       </c>
       <c r="R656" s="6" t="s">
-        <v>2335</v>
+        <v>2343</v>
       </c>
       <c r="S656" s="6" t="s">
-        <v>2336</v>
+        <v>2344</v>
       </c>
       <c r="T656" s="7" t="n">
         <v>45567</v>
@@ -55710,7 +55717,7 @@
         <v>806</v>
       </c>
       <c r="D657" s="6" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
       <c r="E657" s="6" t="s">
         <v>38</v>
@@ -55734,10 +55741,10 @@
         <v>2153</v>
       </c>
       <c r="L657" s="6" t="s">
-        <v>2526</v>
+        <v>2529</v>
       </c>
       <c r="M657" s="6" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
       <c r="N657" s="6"/>
       <c r="O657" s="6" t="s">
@@ -55750,7 +55757,7 @@
         <v>66</v>
       </c>
       <c r="R657" s="6" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="S657" s="6" t="s">
         <v>2157</v>
@@ -55788,10 +55795,10 @@
         <v>35</v>
       </c>
       <c r="C658" s="6" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
       <c r="D658" s="6" t="s">
-        <v>2530</v>
+        <v>2533</v>
       </c>
       <c r="E658" s="6" t="s">
         <v>38</v>
@@ -55800,7 +55807,7 @@
         <v>66571</v>
       </c>
       <c r="G658" s="6" t="s">
-        <v>2531</v>
+        <v>2534</v>
       </c>
       <c r="H658" s="5" t="n">
         <v>72258</v>
@@ -55812,13 +55819,13 @@
         <v>40</v>
       </c>
       <c r="K658" s="6" t="s">
-        <v>2532</v>
+        <v>2535</v>
       </c>
       <c r="L658" s="6" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
       <c r="M658" s="6" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
       <c r="N658" s="6"/>
       <c r="O658" s="6" t="s">
@@ -55831,10 +55838,10 @@
         <v>66</v>
       </c>
       <c r="R658" s="6" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="S658" s="6" t="s">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="T658" s="7" t="n">
         <v>44229</v>
@@ -55873,7 +55880,7 @@
         <v>35</v>
       </c>
       <c r="C659" s="6" t="s">
-        <v>2537</v>
+        <v>2540</v>
       </c>
       <c r="D659" s="6" t="s">
         <v>750</v>
@@ -55885,7 +55892,7 @@
         <v>73516</v>
       </c>
       <c r="G659" s="6" t="s">
-        <v>2538</v>
+        <v>2541</v>
       </c>
       <c r="H659" s="5" t="n">
         <v>70424</v>
@@ -55897,13 +55904,13 @@
         <v>40</v>
       </c>
       <c r="K659" s="6" t="s">
-        <v>2539</v>
+        <v>2542</v>
       </c>
       <c r="L659" s="6" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
       <c r="M659" s="6" t="s">
-        <v>2541</v>
+        <v>2544</v>
       </c>
       <c r="N659" s="6"/>
       <c r="O659" s="6" t="s">
@@ -55916,10 +55923,10 @@
         <v>66</v>
       </c>
       <c r="R659" s="6" t="s">
-        <v>2542</v>
+        <v>2545</v>
       </c>
       <c r="S659" s="6" t="s">
-        <v>2350</v>
+        <v>2358</v>
       </c>
       <c r="T659" s="7" t="n">
         <v>45037</v>
@@ -55954,7 +55961,7 @@
         <v>35</v>
       </c>
       <c r="C660" s="6" t="s">
-        <v>2543</v>
+        <v>2546</v>
       </c>
       <c r="D660" s="6" t="s">
         <v>589</v>
@@ -55966,7 +55973,7 @@
         <v>73516</v>
       </c>
       <c r="G660" s="6" t="s">
-        <v>2544</v>
+        <v>2547</v>
       </c>
       <c r="H660" s="5" t="n">
         <v>73516</v>
@@ -55978,13 +55985,13 @@
         <v>40</v>
       </c>
       <c r="K660" s="6" t="s">
-        <v>2545</v>
+        <v>2548</v>
       </c>
       <c r="L660" s="6" t="s">
-        <v>2546</v>
+        <v>2549</v>
       </c>
       <c r="M660" s="6" t="s">
-        <v>2547</v>
+        <v>2550</v>
       </c>
       <c r="N660" s="6"/>
       <c r="O660" s="6" t="s">
@@ -55997,10 +56004,10 @@
         <v>66</v>
       </c>
       <c r="R660" s="6" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="S660" s="6" t="s">
-        <v>2350</v>
+        <v>2358</v>
       </c>
       <c r="T660" s="7" t="n">
         <v>44254</v>
@@ -56035,10 +56042,10 @@
         <v>35</v>
       </c>
       <c r="C661" s="6" t="s">
-        <v>2337</v>
+        <v>2345</v>
       </c>
       <c r="D661" s="6" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
       <c r="E661" s="6" t="s">
         <v>38</v>
@@ -56047,7 +56054,7 @@
         <v>71700</v>
       </c>
       <c r="G661" s="6" t="s">
-        <v>2550</v>
+        <v>2553</v>
       </c>
       <c r="H661" s="5" t="n">
         <v>71700</v>
@@ -56059,13 +56066,13 @@
         <v>40</v>
       </c>
       <c r="K661" s="6" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="L661" s="6" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
       <c r="M661" s="6" t="s">
-        <v>2553</v>
+        <v>2556</v>
       </c>
       <c r="N661" s="6"/>
       <c r="O661" s="6" t="s">
@@ -56078,10 +56085,10 @@
         <v>66</v>
       </c>
       <c r="R661" s="6" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="S661" s="6" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
       <c r="T661" s="7" t="n">
         <v>43525</v>
@@ -56116,7 +56123,7 @@
         <v>124</v>
       </c>
       <c r="C662" s="6" t="s">
-        <v>2556</v>
+        <v>2559</v>
       </c>
       <c r="D662" s="6" t="s">
         <v>220</v>
@@ -56138,13 +56145,13 @@
         <v>40</v>
       </c>
       <c r="K662" s="6" t="s">
-        <v>2557</v>
+        <v>2560</v>
       </c>
       <c r="L662" s="6" t="s">
-        <v>2558</v>
+        <v>2561</v>
       </c>
       <c r="M662" s="6" t="s">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="N662" s="6"/>
       <c r="O662" s="6" t="s">
@@ -56157,10 +56164,10 @@
         <v>66</v>
       </c>
       <c r="R662" s="6" t="s">
-        <v>2560</v>
+        <v>2563</v>
       </c>
       <c r="S662" s="6" t="s">
-        <v>2377</v>
+        <v>2385</v>
       </c>
       <c r="T662" s="7" t="n">
         <v>43843</v>
@@ -56195,7 +56202,7 @@
         <v>35</v>
       </c>
       <c r="C663" s="6" t="s">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="D663" s="6" t="s">
         <v>362</v>
@@ -56207,7 +56214,7 @@
         <v>71271</v>
       </c>
       <c r="G663" s="6" t="s">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="H663" s="5" t="n">
         <v>71464</v>
@@ -56217,13 +56224,13 @@
       </c>
       <c r="J663" s="6"/>
       <c r="K663" s="6" t="s">
-        <v>2563</v>
+        <v>2566</v>
       </c>
       <c r="L663" s="6" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="M663" s="6" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="N663" s="6"/>
       <c r="O663" s="6" t="s">
@@ -56236,10 +56243,10 @@
         <v>66</v>
       </c>
       <c r="R663" s="6" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
       <c r="S663" s="6" t="s">
-        <v>2567</v>
+        <v>2570</v>
       </c>
       <c r="T663" s="7" t="n">
         <v>42646</v>
@@ -56278,10 +56285,10 @@
         <v>35</v>
       </c>
       <c r="C664" s="6" t="s">
-        <v>2568</v>
+        <v>2571</v>
       </c>
       <c r="D664" s="6" t="s">
-        <v>2569</v>
+        <v>2572</v>
       </c>
       <c r="E664" s="6" t="s">
         <v>38</v>
@@ -56290,7 +56297,7 @@
         <v>73304</v>
       </c>
       <c r="G664" s="6" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="H664" s="5" t="n">
         <v>73304</v>
@@ -56302,13 +56309,13 @@
         <v>40</v>
       </c>
       <c r="K664" s="6" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
       <c r="L664" s="6" t="s">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="M664" s="6" t="s">
-        <v>2573</v>
+        <v>2576</v>
       </c>
       <c r="N664" s="6"/>
       <c r="O664" s="6" t="s">
@@ -56321,10 +56328,10 @@
         <v>66</v>
       </c>
       <c r="R664" s="6" t="s">
-        <v>2574</v>
+        <v>2577</v>
       </c>
       <c r="S664" s="6" t="s">
-        <v>2575</v>
+        <v>2578</v>
       </c>
       <c r="T664" s="7" t="n">
         <v>44561</v>
@@ -56359,10 +56366,10 @@
         <v>124</v>
       </c>
       <c r="C665" s="6" t="s">
-        <v>2576</v>
+        <v>2579</v>
       </c>
       <c r="D665" s="6" t="s">
-        <v>2577</v>
+        <v>2580</v>
       </c>
       <c r="E665" s="6" t="s">
         <v>127</v>
@@ -56371,7 +56378,7 @@
         <v>69437</v>
       </c>
       <c r="G665" s="6" t="s">
-        <v>2193</v>
+        <v>2201</v>
       </c>
       <c r="H665" s="5" t="n">
         <v>68588</v>
@@ -56383,10 +56390,10 @@
         <v>40</v>
       </c>
       <c r="K665" s="6" t="s">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="L665" s="6" t="s">
-        <v>2579</v>
+        <v>2582</v>
       </c>
       <c r="M665" s="6"/>
       <c r="N665" s="6"/>
@@ -56400,10 +56407,10 @@
         <v>469</v>
       </c>
       <c r="R665" s="6" t="s">
-        <v>2580</v>
+        <v>2583</v>
       </c>
       <c r="S665" s="6" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="T665" s="7" t="n">
         <v>42143</v>
@@ -56429,7 +56436,7 @@
       <c r="AG665" s="6"/>
       <c r="AH665" s="8"/>
       <c r="AI665" s="6" t="s">
-        <v>2581</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="666" customHeight="1" ht="20">
@@ -56440,10 +56447,10 @@
         <v>124</v>
       </c>
       <c r="C666" s="6" t="s">
-        <v>2582</v>
+        <v>2585</v>
       </c>
       <c r="D666" s="6" t="s">
-        <v>2583</v>
+        <v>2586</v>
       </c>
       <c r="E666" s="6" t="s">
         <v>127</v>
@@ -56452,7 +56459,7 @@
         <v>73580</v>
       </c>
       <c r="G666" s="6" t="s">
-        <v>2584</v>
+        <v>2587</v>
       </c>
       <c r="H666" s="5" t="n">
         <v>69217</v>
@@ -56463,10 +56470,10 @@
       <c r="J666" s="6"/>
       <c r="K666" s="6"/>
       <c r="L666" s="6" t="s">
-        <v>2585</v>
+        <v>2588</v>
       </c>
       <c r="M666" s="6" t="s">
-        <v>2586</v>
+        <v>2589</v>
       </c>
       <c r="N666" s="6"/>
       <c r="O666" s="6" t="s">
@@ -56479,10 +56486,10 @@
         <v>66</v>
       </c>
       <c r="R666" s="6" t="s">
-        <v>2587</v>
+        <v>2590</v>
       </c>
       <c r="S666" s="6" t="s">
-        <v>2588</v>
+        <v>2591</v>
       </c>
       <c r="T666" s="7" t="n">
         <v>44133</v>
@@ -56517,7 +56524,7 @@
         <v>124</v>
       </c>
       <c r="C667" s="6" t="s">
-        <v>2261</v>
+        <v>2269</v>
       </c>
       <c r="D667" s="6" t="s">
         <v>302</v>
@@ -56529,7 +56536,7 @@
         <v>69720</v>
       </c>
       <c r="G667" s="6" t="s">
-        <v>2175</v>
+        <v>2183</v>
       </c>
       <c r="H667" s="5" t="n">
         <v>72707</v>
@@ -56541,13 +56548,13 @@
         <v>40</v>
       </c>
       <c r="K667" s="6" t="s">
-        <v>2589</v>
+        <v>2592</v>
       </c>
       <c r="L667" s="6" t="s">
-        <v>2590</v>
+        <v>2593</v>
       </c>
       <c r="M667" s="6" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
       <c r="N667" s="6"/>
       <c r="O667" s="6" t="s">
@@ -56560,10 +56567,10 @@
         <v>66</v>
       </c>
       <c r="R667" s="6" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
       <c r="S667" s="6" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
       <c r="T667" s="7" t="n">
         <v>42761</v>
@@ -56602,10 +56609,10 @@
         <v>124</v>
       </c>
       <c r="C668" s="6" t="s">
-        <v>2594</v>
+        <v>2597</v>
       </c>
       <c r="D668" s="6" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="E668" s="6" t="s">
         <v>127</v>
@@ -56614,7 +56621,7 @@
         <v>71271</v>
       </c>
       <c r="G668" s="6" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
       <c r="H668" s="5" t="n">
         <v>76090</v>
@@ -56627,10 +56634,10 @@
       </c>
       <c r="K668" s="6"/>
       <c r="L668" s="6" t="s">
-        <v>2597</v>
+        <v>2600</v>
       </c>
       <c r="M668" s="6" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
       <c r="N668" s="6"/>
       <c r="O668" s="6" t="s">
@@ -56643,10 +56650,10 @@
         <v>66</v>
       </c>
       <c r="R668" s="6" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
       <c r="S668" s="6" t="s">
-        <v>2567</v>
+        <v>2570</v>
       </c>
       <c r="T668" s="7" t="n">
         <v>42646</v>
@@ -56685,7 +56692,7 @@
         <v>35</v>
       </c>
       <c r="C669" s="6" t="s">
-        <v>2600</v>
+        <v>2603</v>
       </c>
       <c r="D669" s="6" t="s">
         <v>524</v>
@@ -56697,7 +56704,7 @@
         <v>71101</v>
       </c>
       <c r="G669" s="6" t="s">
-        <v>2601</v>
+        <v>2604</v>
       </c>
       <c r="H669" s="5" t="n">
         <v>70933</v>
@@ -56707,13 +56714,13 @@
       </c>
       <c r="J669" s="6"/>
       <c r="K669" s="6" t="s">
-        <v>2602</v>
+        <v>2605</v>
       </c>
       <c r="L669" s="6" t="s">
-        <v>2603</v>
+        <v>2606</v>
       </c>
       <c r="M669" s="6" t="s">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="N669" s="6"/>
       <c r="O669" s="6" t="s">
@@ -56726,10 +56733,10 @@
         <v>66</v>
       </c>
       <c r="R669" s="6" t="s">
-        <v>2605</v>
+        <v>2608</v>
       </c>
       <c r="S669" s="6" t="s">
-        <v>2606</v>
+        <v>2609</v>
       </c>
       <c r="T669" s="7" t="n">
         <v>42504</v>
@@ -56759,7 +56766,7 @@
         <v>45831.8282060185</v>
       </c>
       <c r="AI669" s="6" t="s">
-        <v>2607</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="670" customHeight="1" ht="20">
@@ -56770,7 +56777,7 @@
         <v>35</v>
       </c>
       <c r="C670" s="6" t="s">
-        <v>2608</v>
+        <v>2611</v>
       </c>
       <c r="D670" s="6" t="s">
         <v>966</v>
@@ -56782,7 +56789,7 @@
         <v>73304</v>
       </c>
       <c r="G670" s="6" t="s">
-        <v>2609</v>
+        <v>2612</v>
       </c>
       <c r="H670" s="5" t="n">
         <v>76110</v>
@@ -56794,13 +56801,13 @@
         <v>40</v>
       </c>
       <c r="K670" s="6" t="s">
-        <v>2610</v>
+        <v>2613</v>
       </c>
       <c r="L670" s="6" t="s">
-        <v>2611</v>
+        <v>2614</v>
       </c>
       <c r="M670" s="6" t="s">
-        <v>2612</v>
+        <v>2615</v>
       </c>
       <c r="N670" s="6"/>
       <c r="O670" s="6" t="s">
@@ -56813,10 +56820,10 @@
         <v>66</v>
       </c>
       <c r="R670" s="6" t="s">
-        <v>2613</v>
+        <v>2616</v>
       </c>
       <c r="S670" s="6" t="s">
-        <v>2377</v>
+        <v>2385</v>
       </c>
       <c r="T670" s="7" t="n">
         <v>44951</v>
@@ -56855,7 +56862,7 @@
         <v>35</v>
       </c>
       <c r="C671" s="6" t="s">
-        <v>2614</v>
+        <v>2617</v>
       </c>
       <c r="D671" s="6" t="s">
         <v>101</v>
@@ -56867,7 +56874,7 @@
         <v>71475</v>
       </c>
       <c r="G671" s="6" t="s">
-        <v>2615</v>
+        <v>2618</v>
       </c>
       <c r="H671" s="5" t="n">
         <v>71475</v>
@@ -56879,13 +56886,13 @@
         <v>40</v>
       </c>
       <c r="K671" s="6" t="s">
-        <v>2616</v>
+        <v>2619</v>
       </c>
       <c r="L671" s="6" t="s">
-        <v>2617</v>
+        <v>2620</v>
       </c>
       <c r="M671" s="6" t="s">
-        <v>2618</v>
+        <v>2621</v>
       </c>
       <c r="N671" s="6"/>
       <c r="O671" s="6" t="s">
@@ -56898,10 +56905,10 @@
         <v>66</v>
       </c>
       <c r="R671" s="6" t="s">
-        <v>2619</v>
+        <v>2622</v>
       </c>
       <c r="S671" s="6" t="s">
-        <v>2620</v>
+        <v>2623</v>
       </c>
       <c r="T671" s="7" t="n">
         <v>42910</v>
@@ -56936,7 +56943,7 @@
         <v>35</v>
       </c>
       <c r="C672" s="6" t="s">
-        <v>2621</v>
+        <v>2624</v>
       </c>
       <c r="D672" s="6" t="s">
         <v>1488</v>
@@ -56948,7 +56955,7 @@
         <v>73528</v>
       </c>
       <c r="G672" s="6" t="s">
-        <v>2622</v>
+        <v>2625</v>
       </c>
       <c r="H672" s="5" t="n">
         <v>70627</v>
@@ -56960,13 +56967,13 @@
         <v>40</v>
       </c>
       <c r="K672" s="6" t="s">
-        <v>2623</v>
+        <v>2626</v>
       </c>
       <c r="L672" s="6" t="s">
-        <v>2624</v>
+        <v>2627</v>
       </c>
       <c r="M672" s="6" t="s">
-        <v>2625</v>
+        <v>2628</v>
       </c>
       <c r="N672" s="6"/>
       <c r="O672" s="6" t="s">
@@ -56979,10 +56986,10 @@
         <v>66</v>
       </c>
       <c r="R672" s="6" t="s">
-        <v>2626</v>
+        <v>2629</v>
       </c>
       <c r="S672" s="6" t="s">
-        <v>2627</v>
+        <v>2630</v>
       </c>
       <c r="T672" s="7" t="n">
         <v>43251</v>
@@ -57017,10 +57024,10 @@
         <v>124</v>
       </c>
       <c r="C673" s="6" t="s">
-        <v>2628</v>
+        <v>2631</v>
       </c>
       <c r="D673" s="6" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="E673" s="6" t="s">
         <v>127</v>
@@ -57029,7 +57036,7 @@
         <v>68362</v>
       </c>
       <c r="G673" s="6" t="s">
-        <v>2280</v>
+        <v>2288</v>
       </c>
       <c r="H673" s="5" t="n">
         <v>73549</v>
@@ -57041,13 +57048,13 @@
         <v>40</v>
       </c>
       <c r="K673" s="6" t="s">
-        <v>2629</v>
+        <v>2632</v>
       </c>
       <c r="L673" s="6" t="s">
-        <v>2630</v>
+        <v>2633</v>
       </c>
       <c r="M673" s="6" t="s">
-        <v>2631</v>
+        <v>2634</v>
       </c>
       <c r="N673" s="6"/>
       <c r="O673" s="6" t="s">
@@ -57060,10 +57067,10 @@
         <v>66</v>
       </c>
       <c r="R673" s="6" t="s">
-        <v>2632</v>
+        <v>2635</v>
       </c>
       <c r="S673" s="6" t="s">
-        <v>2633</v>
+        <v>2636</v>
       </c>
       <c r="T673" s="7" t="n">
         <v>44399</v>
@@ -57098,7 +57105,7 @@
         <v>35</v>
       </c>
       <c r="C674" s="6" t="s">
-        <v>2634</v>
+        <v>2637</v>
       </c>
       <c r="D674" s="6" t="s">
         <v>348</v>
@@ -57110,7 +57117,7 @@
         <v>69135</v>
       </c>
       <c r="G674" s="6" t="s">
-        <v>2287</v>
+        <v>2295</v>
       </c>
       <c r="H674" s="5" t="n">
         <v>68588</v>
@@ -57122,13 +57129,13 @@
         <v>40</v>
       </c>
       <c r="K674" s="6" t="s">
-        <v>2635</v>
+        <v>2638</v>
       </c>
       <c r="L674" s="6" t="s">
-        <v>2289</v>
+        <v>2297</v>
       </c>
       <c r="M674" s="6" t="s">
-        <v>2636</v>
+        <v>2639</v>
       </c>
       <c r="N674" s="6"/>
       <c r="O674" s="6" t="s">
@@ -57141,10 +57148,10 @@
         <v>66</v>
       </c>
       <c r="R674" s="6" t="s">
-        <v>2637</v>
+        <v>2640</v>
       </c>
       <c r="S674" s="6" t="s">
-        <v>2638</v>
+        <v>2641</v>
       </c>
       <c r="T674" s="7" t="n">
         <v>44578</v>
@@ -57191,7 +57198,7 @@
         <v>65908</v>
       </c>
       <c r="G675" s="6" t="s">
-        <v>2639</v>
+        <v>2642</v>
       </c>
       <c r="H675" s="5" t="n">
         <v>68435</v>
@@ -57204,10 +57211,10 @@
       </c>
       <c r="K675" s="6"/>
       <c r="L675" s="6" t="s">
-        <v>2640</v>
+        <v>2643</v>
       </c>
       <c r="M675" s="6" t="s">
-        <v>2641</v>
+        <v>2644</v>
       </c>
       <c r="N675" s="6"/>
       <c r="O675" s="6" t="s">
@@ -57220,10 +57227,10 @@
         <v>66</v>
       </c>
       <c r="R675" s="6" t="s">
-        <v>2642</v>
+        <v>2645</v>
       </c>
       <c r="S675" s="6" t="s">
-        <v>2643</v>
+        <v>2646</v>
       </c>
       <c r="T675" s="7" t="n">
         <v>44336</v>
@@ -57270,7 +57277,7 @@
         <v>65908</v>
       </c>
       <c r="G676" s="6" t="s">
-        <v>2639</v>
+        <v>2642</v>
       </c>
       <c r="H676" s="5" t="n">
         <v>68435</v>
@@ -57282,13 +57289,13 @@
         <v>40</v>
       </c>
       <c r="K676" s="6" t="s">
-        <v>2644</v>
+        <v>2647</v>
       </c>
       <c r="L676" s="6" t="s">
-        <v>2645</v>
+        <v>2648</v>
       </c>
       <c r="M676" s="6" t="s">
-        <v>2646</v>
+        <v>2649</v>
       </c>
       <c r="N676" s="6"/>
       <c r="O676" s="6" t="s">
@@ -57301,10 +57308,10 @@
         <v>66</v>
       </c>
       <c r="R676" s="6" t="s">
-        <v>2647</v>
+        <v>2650</v>
       </c>
       <c r="S676" s="6" t="s">
-        <v>2648</v>
+        <v>2651</v>
       </c>
       <c r="T676" s="7" t="n">
         <v>45075</v>
@@ -57343,7 +57350,7 @@
         <v>35</v>
       </c>
       <c r="C677" s="6" t="s">
-        <v>2649</v>
+        <v>2652</v>
       </c>
       <c r="D677" s="6" t="s">
         <v>1294</v>
@@ -57355,7 +57362,7 @@
         <v>73084</v>
       </c>
       <c r="G677" s="6" t="s">
-        <v>2650</v>
+        <v>2653</v>
       </c>
       <c r="H677" s="5" t="n">
         <v>73671</v>
@@ -57367,13 +57374,13 @@
         <v>40</v>
       </c>
       <c r="K677" s="6" t="s">
-        <v>2651</v>
+        <v>2654</v>
       </c>
       <c r="L677" s="6" t="s">
-        <v>2652</v>
+        <v>2655</v>
       </c>
       <c r="M677" s="6" t="s">
-        <v>2653</v>
+        <v>2656</v>
       </c>
       <c r="N677" s="6"/>
       <c r="O677" s="6" t="s">
@@ -57386,7 +57393,7 @@
         <v>66</v>
       </c>
       <c r="R677" s="6" t="s">
-        <v>2654</v>
+        <v>2657</v>
       </c>
       <c r="S677" s="6" t="s">
         <v>1391</v>
@@ -57448,13 +57455,13 @@
         <v>40</v>
       </c>
       <c r="K678" s="6" t="s">
-        <v>2655</v>
+        <v>2658</v>
       </c>
       <c r="L678" s="6" t="s">
-        <v>2656</v>
+        <v>2659</v>
       </c>
       <c r="M678" s="6" t="s">
-        <v>2657</v>
+        <v>2660</v>
       </c>
       <c r="N678" s="6"/>
       <c r="O678" s="6" t="s">
@@ -57467,7 +57474,7 @@
         <v>66</v>
       </c>
       <c r="R678" s="6" t="s">
-        <v>2658</v>
+        <v>2661</v>
       </c>
       <c r="S678" s="6" t="s">
         <v>1715</v>
@@ -57517,7 +57524,7 @@
         <v>69398</v>
       </c>
       <c r="G679" s="6" t="s">
-        <v>2659</v>
+        <v>2662</v>
       </c>
       <c r="H679" s="5" t="n">
         <v>69863</v>
@@ -57529,13 +57536,13 @@
         <v>40</v>
       </c>
       <c r="K679" s="6" t="s">
-        <v>2660</v>
+        <v>2663</v>
       </c>
       <c r="L679" s="6" t="s">
-        <v>2661</v>
+        <v>2664</v>
       </c>
       <c r="M679" s="6" t="s">
-        <v>2662</v>
+        <v>2665</v>
       </c>
       <c r="N679" s="6"/>
       <c r="O679" s="6" t="s">
@@ -57548,10 +57555,10 @@
         <v>66</v>
       </c>
       <c r="R679" s="6" t="s">
-        <v>2663</v>
+        <v>2666</v>
       </c>
       <c r="S679" s="6" t="s">
-        <v>2664</v>
+        <v>2667</v>
       </c>
       <c r="T679" s="7" t="n">
         <v>44282</v>
@@ -57590,7 +57597,7 @@
         <v>124</v>
       </c>
       <c r="C680" s="6" t="s">
-        <v>2665</v>
+        <v>2668</v>
       </c>
       <c r="D680" s="6" t="s">
         <v>210</v>
@@ -57602,7 +57609,7 @@
         <v>69398</v>
       </c>
       <c r="G680" s="6" t="s">
-        <v>2659</v>
+        <v>2662</v>
       </c>
       <c r="H680" s="5" t="n">
         <v>67133</v>
@@ -57614,13 +57621,13 @@
         <v>40</v>
       </c>
       <c r="K680" s="6" t="s">
-        <v>2666</v>
+        <v>2669</v>
       </c>
       <c r="L680" s="6" t="s">
-        <v>2667</v>
+        <v>2670</v>
       </c>
       <c r="M680" s="6" t="s">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="N680" s="6"/>
       <c r="O680" s="6" t="s">
@@ -57633,10 +57640,10 @@
         <v>66</v>
       </c>
       <c r="R680" s="6" t="s">
-        <v>2669</v>
+        <v>2672</v>
       </c>
       <c r="S680" s="6" t="s">
-        <v>2664</v>
+        <v>2667</v>
       </c>
       <c r="T680" s="7" t="n">
         <v>44282</v>
@@ -57683,7 +57690,7 @@
         <v>71334</v>
       </c>
       <c r="G681" s="6" t="s">
-        <v>2670</v>
+        <v>2673</v>
       </c>
       <c r="H681" s="5" t="n">
         <v>71501</v>
@@ -57695,13 +57702,13 @@
         <v>40</v>
       </c>
       <c r="K681" s="6" t="s">
-        <v>2671</v>
+        <v>2674</v>
       </c>
       <c r="L681" s="6" t="s">
         <v>1877</v>
       </c>
       <c r="M681" s="6" t="s">
-        <v>2672</v>
+        <v>2675</v>
       </c>
       <c r="N681" s="6"/>
       <c r="O681" s="6" t="s">
@@ -57714,10 +57721,10 @@
         <v>469</v>
       </c>
       <c r="R681" s="6" t="s">
-        <v>2673</v>
+        <v>2676</v>
       </c>
       <c r="S681" s="6" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="T681" s="7" t="n">
         <v>44015</v>
@@ -57759,7 +57766,7 @@
         <v>373</v>
       </c>
       <c r="D682" s="6" t="s">
-        <v>2674</v>
+        <v>2677</v>
       </c>
       <c r="E682" s="6" t="s">
         <v>127</v>
@@ -57768,7 +57775,7 @@
         <v>71334</v>
       </c>
       <c r="G682" s="6" t="s">
-        <v>2675</v>
+        <v>2678</v>
       </c>
       <c r="H682" s="5" t="n">
         <v>71501</v>
@@ -57780,13 +57787,13 @@
         <v>40</v>
       </c>
       <c r="K682" s="6" t="s">
-        <v>2676</v>
+        <v>2679</v>
       </c>
       <c r="L682" s="6" t="s">
         <v>1877</v>
       </c>
       <c r="M682" s="6" t="s">
-        <v>2677</v>
+        <v>2680</v>
       </c>
       <c r="N682" s="6"/>
       <c r="O682" s="6" t="s">
@@ -57799,10 +57806,10 @@
         <v>66</v>
       </c>
       <c r="R682" s="6" t="s">
-        <v>2678</v>
+        <v>2681</v>
       </c>
       <c r="S682" s="6" t="s">
-        <v>2679</v>
+        <v>2682</v>
       </c>
       <c r="T682" s="7" t="n">
         <v>45716</v>
@@ -57837,10 +57844,10 @@
         <v>124</v>
       </c>
       <c r="C683" s="6" t="s">
-        <v>2680</v>
+        <v>2683</v>
       </c>
       <c r="D683" s="6" t="s">
-        <v>2681</v>
+        <v>2684</v>
       </c>
       <c r="E683" s="6" t="s">
         <v>127</v>
@@ -57849,7 +57856,7 @@
         <v>67226</v>
       </c>
       <c r="G683" s="6" t="s">
-        <v>2212</v>
+        <v>2220</v>
       </c>
       <c r="H683" s="5" t="n">
         <v>70262</v>
@@ -57861,13 +57868,13 @@
         <v>40</v>
       </c>
       <c r="K683" s="6" t="s">
-        <v>2682</v>
+        <v>2685</v>
       </c>
       <c r="L683" s="6" t="s">
-        <v>2683</v>
+        <v>2686</v>
       </c>
       <c r="M683" s="6" t="s">
-        <v>2684</v>
+        <v>2687</v>
       </c>
       <c r="N683" s="6"/>
       <c r="O683" s="6" t="s">
@@ -57880,10 +57887,10 @@
         <v>66</v>
       </c>
       <c r="R683" s="6" t="s">
-        <v>2685</v>
+        <v>2688</v>
       </c>
       <c r="S683" s="6" t="s">
-        <v>2217</v>
+        <v>2225</v>
       </c>
       <c r="T683" s="7" t="n">
         <v>44413</v>
@@ -57918,7 +57925,7 @@
         <v>35</v>
       </c>
       <c r="C684" s="6" t="s">
-        <v>2686</v>
+        <v>2689</v>
       </c>
       <c r="D684" s="6" t="s">
         <v>547</v>
@@ -57930,7 +57937,7 @@
         <v>70765</v>
       </c>
       <c r="G684" s="6" t="s">
-        <v>2687</v>
+        <v>2690</v>
       </c>
       <c r="H684" s="5" t="n">
         <v>69863</v>
@@ -57942,13 +57949,13 @@
         <v>40</v>
       </c>
       <c r="K684" s="6" t="s">
-        <v>2688</v>
+        <v>2691</v>
       </c>
       <c r="L684" s="6" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="M684" s="6" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="N684" s="6"/>
       <c r="O684" s="6" t="s">
@@ -57961,10 +57968,10 @@
         <v>66</v>
       </c>
       <c r="R684" s="6" t="s">
-        <v>2691</v>
+        <v>2694</v>
       </c>
       <c r="S684" s="6" t="s">
-        <v>2692</v>
+        <v>2695</v>
       </c>
       <c r="T684" s="7" t="n">
         <v>45274</v>
@@ -57999,7 +58006,7 @@
         <v>124</v>
       </c>
       <c r="C685" s="6" t="s">
-        <v>2693</v>
+        <v>2696</v>
       </c>
       <c r="D685" s="6" t="s">
         <v>220</v>
@@ -58011,7 +58018,7 @@
         <v>71126</v>
       </c>
       <c r="G685" s="6" t="s">
-        <v>2694</v>
+        <v>2697</v>
       </c>
       <c r="H685" s="5" t="n">
         <v>69863</v>
@@ -58023,13 +58030,13 @@
         <v>40</v>
       </c>
       <c r="K685" s="6" t="s">
-        <v>2695</v>
+        <v>2698</v>
       </c>
       <c r="L685" s="6" t="s">
-        <v>2696</v>
+        <v>2699</v>
       </c>
       <c r="M685" s="6" t="s">
-        <v>2697</v>
+        <v>2700</v>
       </c>
       <c r="N685" s="6"/>
       <c r="O685" s="6" t="s">
@@ -58042,10 +58049,10 @@
         <v>66</v>
       </c>
       <c r="R685" s="6" t="s">
-        <v>2698</v>
+        <v>2701</v>
       </c>
       <c r="S685" s="6" t="s">
-        <v>2699</v>
+        <v>2702</v>
       </c>
       <c r="T685" s="7" t="n">
         <v>45016</v>
@@ -58071,7 +58078,7 @@
       <c r="AG685" s="6"/>
       <c r="AH685" s="8"/>
       <c r="AI685" s="6" t="s">
-        <v>2700</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="686" customHeight="1" ht="20">
@@ -58106,13 +58113,13 @@
         <v>40</v>
       </c>
       <c r="K686" s="6" t="s">
-        <v>2701</v>
+        <v>2704</v>
       </c>
       <c r="L686" s="6" t="s">
-        <v>2702</v>
+        <v>2705</v>
       </c>
       <c r="M686" s="6" t="s">
-        <v>2703</v>
+        <v>2706</v>
       </c>
       <c r="N686" s="6"/>
       <c r="O686" s="6" t="s">
@@ -58125,10 +58132,10 @@
         <v>66</v>
       </c>
       <c r="R686" s="6" t="s">
-        <v>2704</v>
+        <v>2707</v>
       </c>
       <c r="S686" s="6" t="s">
-        <v>2705</v>
+        <v>2708</v>
       </c>
       <c r="T686" s="7" t="n">
         <v>45049</v>
@@ -58175,7 +58182,7 @@
         <v>72753</v>
       </c>
       <c r="G687" s="6" t="s">
-        <v>2706</v>
+        <v>2709</v>
       </c>
       <c r="H687" s="5" t="n">
         <v>67941</v>
@@ -58187,13 +58194,13 @@
         <v>40</v>
       </c>
       <c r="K687" s="6" t="s">
-        <v>2707</v>
+        <v>2710</v>
       </c>
       <c r="L687" s="6" t="s">
-        <v>2708</v>
+        <v>2711</v>
       </c>
       <c r="M687" s="6" t="s">
-        <v>2709</v>
+        <v>2712</v>
       </c>
       <c r="N687" s="6"/>
       <c r="O687" s="6" t="s">
@@ -58206,10 +58213,10 @@
         <v>66</v>
       </c>
       <c r="R687" s="6" t="s">
-        <v>2710</v>
+        <v>2713</v>
       </c>
       <c r="S687" s="6" t="s">
-        <v>2711</v>
+        <v>2714</v>
       </c>
       <c r="T687" s="7" t="n">
         <v>43500</v>
